--- a/registros.xlsx
+++ b/registros.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA870"/>
+  <dimension ref="A1:AA877"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -47877,16 +47877,513 @@
         <v>{"Fecha":"2026-09-07","Observaciones":"Termina trasiego","Hora":"07:39","Encargado":"Jorge mario Cadavid gallego","PlacaCisterna":"Jrr799"}</v>
       </c>
     </row>
+    <row r="871">
+      <c r="A871">
+        <v>64</v>
+      </c>
+      <c r="B871">
+        <v>100</v>
+      </c>
+      <c r="C871">
+        <v>19</v>
+      </c>
+      <c r="D871">
+        <v>40</v>
+      </c>
+      <c r="E871">
+        <v>110</v>
+      </c>
+      <c r="F871">
+        <v>22</v>
+      </c>
+      <c r="G871">
+        <v>10561</v>
+      </c>
+      <c r="H871" t="str">
+        <v>Jrr</v>
+      </c>
+      <c r="I871">
+        <v>115</v>
+      </c>
+      <c r="J871">
+        <v>56</v>
+      </c>
+      <c r="K871">
+        <v>110</v>
+      </c>
+      <c r="L871">
+        <v>11</v>
+      </c>
+      <c r="O871" t="str">
+        <v>Ninguna</v>
+      </c>
+      <c r="P871" t="str">
+        <v>Jorge mario Cadavid gallego</v>
+      </c>
+      <c r="Q871" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="R871" t="str">
+        <v>12:36:00</v>
+      </c>
+      <c r="U871">
+        <v>1788802697016</v>
+      </c>
+      <c r="V871" t="str">
+        <v>2026-09-07T17:38:17.016Z</v>
+      </c>
+      <c r="W871" t="str">
+        <v>07/09/2026, 12:38:17</v>
+      </c>
+      <c r="X871">
+        <v>2</v>
+      </c>
+      <c r="Y871">
+        <v>11</v>
+      </c>
+      <c r="Z871">
+        <v>11</v>
+      </c>
+      <c r="AA871" t="str">
+        <v>{"Hora":"12:36","Observaciones":"Ninguna","Fecha":"2026-09-07","Encargado":"Jorge mario Cadavid gallego","PlacaCisterna":"Jrr"}</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872">
+        <v>52</v>
+      </c>
+      <c r="B872">
+        <v>100</v>
+      </c>
+      <c r="C872">
+        <v>40</v>
+      </c>
+      <c r="D872">
+        <v>20</v>
+      </c>
+      <c r="E872">
+        <v>110</v>
+      </c>
+      <c r="F872">
+        <v>22</v>
+      </c>
+      <c r="G872">
+        <v>14000</v>
+      </c>
+      <c r="H872" t="str">
+        <v>Jrr-799</v>
+      </c>
+      <c r="I872">
+        <v>110</v>
+      </c>
+      <c r="J872">
+        <v>54</v>
+      </c>
+      <c r="K872">
+        <v>105</v>
+      </c>
+      <c r="L872">
+        <v>11</v>
+      </c>
+      <c r="O872" t="str">
+        <v/>
+      </c>
+      <c r="P872" t="str">
+        <v>Jiovanny Montoya Monroy</v>
+      </c>
+      <c r="Q872" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="R872" t="str">
+        <v>15:04:00</v>
+      </c>
+      <c r="U872">
+        <v>1788811659043</v>
+      </c>
+      <c r="V872" t="str">
+        <v>2026-09-07T20:07:39.043Z</v>
+      </c>
+      <c r="W872" t="str">
+        <v>07/09/2026, 15:07:39</v>
+      </c>
+      <c r="X872">
+        <v>4</v>
+      </c>
+      <c r="Y872">
+        <v>11</v>
+      </c>
+      <c r="Z872">
+        <v>11</v>
+      </c>
+      <c r="AA872" t="str">
+        <v>{"Fecha":"2026-09-07","Hora":"15:04","PlacaCisterna":"Jrr-799","Observaciones":"","Encargado":"Jiovanny Montoya Monroy"}</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873">
+        <v>42</v>
+      </c>
+      <c r="B873">
+        <v>100</v>
+      </c>
+      <c r="C873">
+        <v>20</v>
+      </c>
+      <c r="D873">
+        <v>40</v>
+      </c>
+      <c r="E873">
+        <v>110</v>
+      </c>
+      <c r="F873">
+        <v>22</v>
+      </c>
+      <c r="G873">
+        <v>14000</v>
+      </c>
+      <c r="H873" t="str">
+        <v>Jrr-799</v>
+      </c>
+      <c r="I873">
+        <v>110</v>
+      </c>
+      <c r="J873">
+        <v>55</v>
+      </c>
+      <c r="K873">
+        <v>110</v>
+      </c>
+      <c r="L873">
+        <v>11</v>
+      </c>
+      <c r="O873" t="str">
+        <v/>
+      </c>
+      <c r="P873" t="str">
+        <v>Jiovanny Montoya Monroy</v>
+      </c>
+      <c r="Q873" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="R873" t="str">
+        <v>16:51:00</v>
+      </c>
+      <c r="U873">
+        <v>1788817977777</v>
+      </c>
+      <c r="V873" t="str">
+        <v>2026-09-07T21:52:57.777Z</v>
+      </c>
+      <c r="W873" t="str">
+        <v>07/09/2026, 16:52:57</v>
+      </c>
+      <c r="X873">
+        <v>2</v>
+      </c>
+      <c r="Y873">
+        <v>11</v>
+      </c>
+      <c r="Z873">
+        <v>11</v>
+      </c>
+      <c r="AA873" t="str">
+        <v>{"PlacaCisterna":"Jrr-799","Encargado":"Jiovanny Montoya Monroy","Hora":"16:51","Observaciones":"","Fecha":"2026-09-07"}</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874">
+        <v>87</v>
+      </c>
+      <c r="B874">
+        <v>100</v>
+      </c>
+      <c r="C874">
+        <v>19</v>
+      </c>
+      <c r="D874">
+        <v>0</v>
+      </c>
+      <c r="E874">
+        <v>90</v>
+      </c>
+      <c r="F874">
+        <v>22</v>
+      </c>
+      <c r="G874">
+        <v>0</v>
+      </c>
+      <c r="H874" t="str">
+        <v>0</v>
+      </c>
+      <c r="I874">
+        <v>110</v>
+      </c>
+      <c r="J874">
+        <v>60</v>
+      </c>
+      <c r="K874">
+        <v>110</v>
+      </c>
+      <c r="L874">
+        <v>10</v>
+      </c>
+      <c r="O874" t="str">
+        <v/>
+      </c>
+      <c r="P874" t="str">
+        <v>KEINER DE HORTA</v>
+      </c>
+      <c r="Q874" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="R874" t="str">
+        <v>20:07:00</v>
+      </c>
+      <c r="U874">
+        <v>1788829671341</v>
+      </c>
+      <c r="V874" t="str">
+        <v>2026-09-08T01:07:51.341Z</v>
+      </c>
+      <c r="W874" t="str">
+        <v>07/09/2026, 20:07:51</v>
+      </c>
+      <c r="X874">
+        <v>1</v>
+      </c>
+      <c r="Y874">
+        <v>11</v>
+      </c>
+      <c r="Z874">
+        <v>11</v>
+      </c>
+      <c r="AA874" t="str">
+        <v>{"PlacaCisterna":"0","Fecha":"2026-09-07","Hora":"20:07","Encargado":"KEINER DE HORTA","Observaciones":""}</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875">
+        <v>72</v>
+      </c>
+      <c r="B875">
+        <v>100</v>
+      </c>
+      <c r="C875">
+        <v>19</v>
+      </c>
+      <c r="D875">
+        <v>0</v>
+      </c>
+      <c r="E875">
+        <v>0</v>
+      </c>
+      <c r="F875">
+        <v>0</v>
+      </c>
+      <c r="G875">
+        <v>0</v>
+      </c>
+      <c r="H875" t="str">
+        <v>0</v>
+      </c>
+      <c r="I875">
+        <v>110</v>
+      </c>
+      <c r="J875">
+        <v>52</v>
+      </c>
+      <c r="K875">
+        <v>105</v>
+      </c>
+      <c r="L875">
+        <v>12</v>
+      </c>
+      <c r="O875" t="str">
+        <v xml:space="preserve">Ningúna </v>
+      </c>
+      <c r="P875" t="str">
+        <v>Edison Giraldo Isaza</v>
+      </c>
+      <c r="Q875" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="R875" t="str">
+        <v>23:50:00</v>
+      </c>
+      <c r="U875">
+        <v>1788844236328</v>
+      </c>
+      <c r="V875" t="str">
+        <v>2026-09-08T05:10:36.328Z</v>
+      </c>
+      <c r="W875" t="str">
+        <v>08/09/2026, 00:10:36</v>
+      </c>
+      <c r="X875">
+        <v>21</v>
+      </c>
+      <c r="Y875">
+        <v>11</v>
+      </c>
+      <c r="Z875">
+        <v>11</v>
+      </c>
+      <c r="AA875" t="str">
+        <v>{"PlacaCisterna":"0","Encargado":"Edison Giraldo Isaza","Fecha":"2026-09-07","Hora":"23:50","Observaciones":"Ningúna "}</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876">
+        <v>55</v>
+      </c>
+      <c r="B876">
+        <v>100</v>
+      </c>
+      <c r="C876">
+        <v>19</v>
+      </c>
+      <c r="D876">
+        <v>0</v>
+      </c>
+      <c r="E876">
+        <v>0</v>
+      </c>
+      <c r="F876">
+        <v>0</v>
+      </c>
+      <c r="G876">
+        <v>0</v>
+      </c>
+      <c r="H876" t="str">
+        <v>0</v>
+      </c>
+      <c r="I876">
+        <v>110</v>
+      </c>
+      <c r="J876">
+        <v>52</v>
+      </c>
+      <c r="K876">
+        <v>105</v>
+      </c>
+      <c r="L876">
+        <v>12</v>
+      </c>
+      <c r="O876" t="str">
+        <v xml:space="preserve">Ningúna </v>
+      </c>
+      <c r="P876" t="str">
+        <v>Edison Giraldo Isaza</v>
+      </c>
+      <c r="Q876" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="R876" t="str">
+        <v>03:49:00</v>
+      </c>
+      <c r="U876">
+        <v>1788857496126</v>
+      </c>
+      <c r="V876" t="str">
+        <v>2026-09-08T08:51:36.126Z</v>
+      </c>
+      <c r="W876" t="str">
+        <v>08/09/2026, 03:51:36</v>
+      </c>
+      <c r="X876">
+        <v>3</v>
+      </c>
+      <c r="Y876">
+        <v>11</v>
+      </c>
+      <c r="Z876">
+        <v>11</v>
+      </c>
+      <c r="AA876" t="str">
+        <v>{"Encargado":"Edison Giraldo Isaza","Fecha":"2026-09-08","Hora":"03:49","Observaciones":"Ningúna ","PlacaCisterna":"0"}</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877">
+        <v>49</v>
+      </c>
+      <c r="B877">
+        <v>100</v>
+      </c>
+      <c r="C877">
+        <v>19</v>
+      </c>
+      <c r="D877">
+        <v>0</v>
+      </c>
+      <c r="E877">
+        <v>0</v>
+      </c>
+      <c r="F877">
+        <v>0</v>
+      </c>
+      <c r="G877">
+        <v>0</v>
+      </c>
+      <c r="H877" t="str">
+        <v>0</v>
+      </c>
+      <c r="I877">
+        <v>110</v>
+      </c>
+      <c r="J877">
+        <v>52</v>
+      </c>
+      <c r="K877">
+        <v>105</v>
+      </c>
+      <c r="L877">
+        <v>12</v>
+      </c>
+      <c r="O877" t="str">
+        <v xml:space="preserve">Ningúna </v>
+      </c>
+      <c r="P877" t="str">
+        <v>Edison Giraldo Isaza</v>
+      </c>
+      <c r="Q877" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="R877" t="str">
+        <v>05:25:00</v>
+      </c>
+      <c r="U877">
+        <v>1788863873587</v>
+      </c>
+      <c r="V877" t="str">
+        <v>2026-09-08T10:37:53.587Z</v>
+      </c>
+      <c r="W877" t="str">
+        <v>08/09/2026, 05:37:53</v>
+      </c>
+      <c r="X877">
+        <v>13</v>
+      </c>
+      <c r="Y877">
+        <v>11</v>
+      </c>
+      <c r="Z877">
+        <v>11</v>
+      </c>
+      <c r="AA877" t="str">
+        <v>{"Hora":"05:25","Observaciones":"Ningúna ","Fecha":"2026-09-08","PlacaCisterna":"0","Encargado":"Edison Giraldo Isaza"}</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA870"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA877"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E870"/>
+  <dimension ref="A1:E877"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -56920,16 +57417,16 @@
         <v>532</v>
       </c>
       <c r="B532" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C532">
-        <v>2</v>
+        <v>532</v>
       </c>
       <c r="D532" t="str">
         <v>T:2026-07-31|T:19:30:00</v>
       </c>
       <c r="E532" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="533">
@@ -56937,16 +57434,16 @@
         <v>533</v>
       </c>
       <c r="B533" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C533">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="D533" t="str">
         <v>T:2026-07-31|T:23:06:00</v>
       </c>
       <c r="E533" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="534">
@@ -56954,16 +57451,16 @@
         <v>534</v>
       </c>
       <c r="B534" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C534">
-        <v>4</v>
+        <v>534</v>
       </c>
       <c r="D534" t="str">
         <v>T:2026-08-01|T:01:33:00</v>
       </c>
       <c r="E534" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="535">
@@ -56971,16 +57468,16 @@
         <v>535</v>
       </c>
       <c r="B535" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C535">
-        <v>5</v>
+        <v>535</v>
       </c>
       <c r="D535" t="str">
         <v>T:2026-08-01|T:03:13:00</v>
       </c>
       <c r="E535" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="536">
@@ -56988,16 +57485,16 @@
         <v>536</v>
       </c>
       <c r="B536" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C536">
-        <v>6</v>
+        <v>536</v>
       </c>
       <c r="D536" t="str">
         <v>T:2026-08-01|T:05:19:00</v>
       </c>
       <c r="E536" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="537">
@@ -57005,16 +57502,16 @@
         <v>537</v>
       </c>
       <c r="B537" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C537">
-        <v>7</v>
+        <v>537</v>
       </c>
       <c r="D537" t="str">
         <v>T:2026-08-01|T:18:20:00</v>
       </c>
       <c r="E537" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="538">
@@ -57022,16 +57519,16 @@
         <v>538</v>
       </c>
       <c r="B538" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C538">
-        <v>8</v>
+        <v>538</v>
       </c>
       <c r="D538" t="str">
         <v>T:2026-08-01|T:21:15:00</v>
       </c>
       <c r="E538" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="539">
@@ -57039,16 +57536,16 @@
         <v>539</v>
       </c>
       <c r="B539" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C539">
-        <v>9</v>
+        <v>539</v>
       </c>
       <c r="D539" t="str">
         <v>T:2026-08-01|T:23:10:00</v>
       </c>
       <c r="E539" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="540">
@@ -57056,16 +57553,16 @@
         <v>540</v>
       </c>
       <c r="B540" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C540">
-        <v>10</v>
+        <v>540</v>
       </c>
       <c r="D540" t="str">
         <v>T:2026-08-02|T:01:08:00</v>
       </c>
       <c r="E540" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="541">
@@ -57073,16 +57570,16 @@
         <v>541</v>
       </c>
       <c r="B541" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C541">
-        <v>11</v>
+        <v>541</v>
       </c>
       <c r="D541" t="str">
         <v>T:2026-08-02|T:03:02:00</v>
       </c>
       <c r="E541" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="542">
@@ -57090,16 +57587,16 @@
         <v>542</v>
       </c>
       <c r="B542" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C542">
-        <v>12</v>
+        <v>542</v>
       </c>
       <c r="D542" t="str">
         <v>T:2026-08-02|T:17:20:00</v>
       </c>
       <c r="E542" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="543">
@@ -57107,16 +57604,16 @@
         <v>543</v>
       </c>
       <c r="B543" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C543">
-        <v>13</v>
+        <v>543</v>
       </c>
       <c r="D543" t="str">
         <v>T:2026-08-02|T:21:00:00</v>
       </c>
       <c r="E543" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="544">
@@ -57124,16 +57621,16 @@
         <v>544</v>
       </c>
       <c r="B544" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C544">
-        <v>14</v>
+        <v>544</v>
       </c>
       <c r="D544" t="str">
         <v>T:2026-08-02|T:23:12:00</v>
       </c>
       <c r="E544" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="545">
@@ -57141,16 +57638,16 @@
         <v>545</v>
       </c>
       <c r="B545" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C545">
-        <v>15</v>
+        <v>545</v>
       </c>
       <c r="D545" t="str">
         <v>T:2026-08-03|T:01:41:00</v>
       </c>
       <c r="E545" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="546">
@@ -57158,16 +57655,16 @@
         <v>546</v>
       </c>
       <c r="B546" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C546">
-        <v>16</v>
+        <v>546</v>
       </c>
       <c r="D546" t="str">
         <v>T:2026-08-03|T:05:25:00</v>
       </c>
       <c r="E546" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="547">
@@ -57175,16 +57672,16 @@
         <v>547</v>
       </c>
       <c r="B547" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C547">
-        <v>17</v>
+        <v>547</v>
       </c>
       <c r="D547" t="str">
         <v>T:2026-08-03|T:14:50:00</v>
       </c>
       <c r="E547" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="548">
@@ -57192,16 +57689,16 @@
         <v>548</v>
       </c>
       <c r="B548" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C548">
-        <v>18</v>
+        <v>548</v>
       </c>
       <c r="D548" t="str">
         <v>T:2026-08-03|T:16:10:00</v>
       </c>
       <c r="E548" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="549">
@@ -57209,16 +57706,16 @@
         <v>549</v>
       </c>
       <c r="B549" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C549">
-        <v>19</v>
+        <v>549</v>
       </c>
       <c r="D549" t="str">
         <v>T:2026-08-03|T:17:15:00</v>
       </c>
       <c r="E549" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="550">
@@ -57226,16 +57723,16 @@
         <v>550</v>
       </c>
       <c r="B550" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C550">
-        <v>20</v>
+        <v>550</v>
       </c>
       <c r="D550" t="str">
         <v>T:2026-08-03|T:19:15:00</v>
       </c>
       <c r="E550" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="551">
@@ -57243,16 +57740,16 @@
         <v>551</v>
       </c>
       <c r="B551" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C551">
-        <v>21</v>
+        <v>551</v>
       </c>
       <c r="D551" t="str">
         <v>T:2026-08-03|T:23:02:00</v>
       </c>
       <c r="E551" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="552">
@@ -57260,16 +57757,16 @@
         <v>552</v>
       </c>
       <c r="B552" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C552">
-        <v>22</v>
+        <v>552</v>
       </c>
       <c r="D552" t="str">
         <v>T:2026-08-04|T:01:20:00</v>
       </c>
       <c r="E552" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="553">
@@ -57277,16 +57774,16 @@
         <v>553</v>
       </c>
       <c r="B553" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C553">
-        <v>23</v>
+        <v>553</v>
       </c>
       <c r="D553" t="str">
         <v>T:2026-08-04|T:03:32:00</v>
       </c>
       <c r="E553" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="554">
@@ -57294,16 +57791,16 @@
         <v>554</v>
       </c>
       <c r="B554" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C554">
-        <v>24</v>
+        <v>554</v>
       </c>
       <c r="D554" t="str">
         <v>T:2026-08-04|T:05:11:00</v>
       </c>
       <c r="E554" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="555">
@@ -57311,16 +57808,16 @@
         <v>555</v>
       </c>
       <c r="B555" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C555">
-        <v>25</v>
+        <v>555</v>
       </c>
       <c r="D555" t="str">
         <v>T:2026-08-04|T:10:28:00</v>
       </c>
       <c r="E555" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="556">
@@ -57328,16 +57825,16 @@
         <v>556</v>
       </c>
       <c r="B556" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C556">
-        <v>26</v>
+        <v>556</v>
       </c>
       <c r="D556" t="str">
         <v>T:2026-08-04|T:11:35:00</v>
       </c>
       <c r="E556" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="557">
@@ -57345,16 +57842,16 @@
         <v>557</v>
       </c>
       <c r="B557" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C557">
-        <v>33</v>
+        <v>557</v>
       </c>
       <c r="D557" t="str">
         <v>T:2026-08-04|T:12:39:00</v>
       </c>
       <c r="E557" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="558">
@@ -57362,16 +57859,16 @@
         <v>558</v>
       </c>
       <c r="B558" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C558">
-        <v>27</v>
+        <v>558</v>
       </c>
       <c r="D558" t="str">
         <v>T:2026-08-04|T:17:29:00</v>
       </c>
       <c r="E558" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="559">
@@ -57379,16 +57876,16 @@
         <v>559</v>
       </c>
       <c r="B559" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C559">
-        <v>28</v>
+        <v>559</v>
       </c>
       <c r="D559" t="str">
         <v>T:2026-08-04|T:19:19:00</v>
       </c>
       <c r="E559" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="560">
@@ -57396,16 +57893,16 @@
         <v>560</v>
       </c>
       <c r="B560" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C560">
-        <v>29</v>
+        <v>560</v>
       </c>
       <c r="D560" t="str">
         <v>T:2026-08-04|T:23:14:00</v>
       </c>
       <c r="E560" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="561">
@@ -57413,16 +57910,16 @@
         <v>561</v>
       </c>
       <c r="B561" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C561">
-        <v>30</v>
+        <v>561</v>
       </c>
       <c r="D561" t="str">
         <v>T:2026-08-05|T:01:18:00</v>
       </c>
       <c r="E561" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="562">
@@ -57430,16 +57927,16 @@
         <v>562</v>
       </c>
       <c r="B562" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C562">
-        <v>31</v>
+        <v>562</v>
       </c>
       <c r="D562" t="str">
         <v>T:2026-08-05|T:03:10:00</v>
       </c>
       <c r="E562" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="563">
@@ -57447,16 +57944,16 @@
         <v>563</v>
       </c>
       <c r="B563" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C563">
-        <v>32</v>
+        <v>563</v>
       </c>
       <c r="D563" t="str">
         <v>T:2026-08-05|T:07:34:00</v>
       </c>
       <c r="E563" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="564">
@@ -57464,16 +57961,16 @@
         <v>564</v>
       </c>
       <c r="B564" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C564">
-        <v>34</v>
+        <v>564</v>
       </c>
       <c r="D564" t="str">
         <v>T:2026-08-05|T:09:40:00</v>
       </c>
       <c r="E564" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="565">
@@ -57481,16 +57978,16 @@
         <v>565</v>
       </c>
       <c r="B565" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C565">
-        <v>35</v>
+        <v>565</v>
       </c>
       <c r="D565" t="str">
         <v>T:2026-08-05|T:10:52:00</v>
       </c>
       <c r="E565" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="566">
@@ -57498,16 +57995,16 @@
         <v>566</v>
       </c>
       <c r="B566" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C566">
-        <v>36</v>
+        <v>566</v>
       </c>
       <c r="D566" t="str">
         <v>T:2026-08-05|T:11:56:00</v>
       </c>
       <c r="E566" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="567">
@@ -57515,16 +58012,16 @@
         <v>567</v>
       </c>
       <c r="B567" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C567">
-        <v>37</v>
+        <v>567</v>
       </c>
       <c r="D567" t="str">
         <v>T:2026-08-05|T:13:32:00</v>
       </c>
       <c r="E567" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="568">
@@ -57532,16 +58029,16 @@
         <v>568</v>
       </c>
       <c r="B568" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C568">
-        <v>38</v>
+        <v>568</v>
       </c>
       <c r="D568" t="str">
         <v>T:2026-08-05|T:15:33:00</v>
       </c>
       <c r="E568" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="569">
@@ -57549,16 +58046,16 @@
         <v>569</v>
       </c>
       <c r="B569" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C569">
-        <v>39</v>
+        <v>569</v>
       </c>
       <c r="D569" t="str">
         <v>T:2026-08-05|T:17:25:00</v>
       </c>
       <c r="E569" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="570">
@@ -57566,16 +58063,16 @@
         <v>570</v>
       </c>
       <c r="B570" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C570">
-        <v>40</v>
+        <v>570</v>
       </c>
       <c r="D570" t="str">
         <v>T:2026-08-05|T:18:40:00</v>
       </c>
       <c r="E570" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="571">
@@ -57583,16 +58080,16 @@
         <v>571</v>
       </c>
       <c r="B571" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C571">
-        <v>41</v>
+        <v>571</v>
       </c>
       <c r="D571" t="str">
         <v>T:2026-08-05|T:20:08:00</v>
       </c>
       <c r="E571" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="572">
@@ -57600,16 +58097,16 @@
         <v>572</v>
       </c>
       <c r="B572" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C572">
-        <v>42</v>
+        <v>572</v>
       </c>
       <c r="D572" t="str">
         <v>T:2026-08-05|T:23:10:00</v>
       </c>
       <c r="E572" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="573">
@@ -57617,16 +58114,16 @@
         <v>573</v>
       </c>
       <c r="B573" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C573">
-        <v>54</v>
+        <v>573</v>
       </c>
       <c r="D573" t="str">
         <v>T:2026-08-06|T:01:49:00</v>
       </c>
       <c r="E573" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="574">
@@ -57634,16 +58131,16 @@
         <v>574</v>
       </c>
       <c r="B574" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C574">
-        <v>43</v>
+        <v>574</v>
       </c>
       <c r="D574" t="str">
         <v>T:2026-08-06|T:01:55:00</v>
       </c>
       <c r="E574" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="575">
@@ -57651,16 +58148,16 @@
         <v>575</v>
       </c>
       <c r="B575" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C575">
-        <v>44</v>
+        <v>575</v>
       </c>
       <c r="D575" t="str">
         <v>T:2026-08-06|T:03:23:00</v>
       </c>
       <c r="E575" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="576">
@@ -57668,16 +58165,16 @@
         <v>576</v>
       </c>
       <c r="B576" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C576">
-        <v>45</v>
+        <v>576</v>
       </c>
       <c r="D576" t="str">
         <v>T:2026-08-06|T:05:15:00</v>
       </c>
       <c r="E576" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="577">
@@ -57685,16 +58182,16 @@
         <v>577</v>
       </c>
       <c r="B577" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C577">
-        <v>46</v>
+        <v>577</v>
       </c>
       <c r="D577" t="str">
         <v>T:2026-08-06|T:07:40:00</v>
       </c>
       <c r="E577" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="578">
@@ -57702,16 +58199,16 @@
         <v>578</v>
       </c>
       <c r="B578" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C578">
-        <v>47</v>
+        <v>578</v>
       </c>
       <c r="D578" t="str">
         <v>T:2026-08-06|T:11:15:00</v>
       </c>
       <c r="E578" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="579">
@@ -57719,16 +58216,16 @@
         <v>579</v>
       </c>
       <c r="B579" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C579">
-        <v>48</v>
+        <v>579</v>
       </c>
       <c r="D579" t="str">
         <v>T:2026-08-06|T:13:09:00</v>
       </c>
       <c r="E579" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="580">
@@ -57736,16 +58233,16 @@
         <v>580</v>
       </c>
       <c r="B580" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C580">
-        <v>49</v>
+        <v>580</v>
       </c>
       <c r="D580" t="str">
         <v>T:2026-08-06|T:15:39:00</v>
       </c>
       <c r="E580" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="581">
@@ -57753,16 +58250,16 @@
         <v>581</v>
       </c>
       <c r="B581" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C581">
-        <v>50</v>
+        <v>581</v>
       </c>
       <c r="D581" t="str">
         <v>T:2026-08-06|T:17:20:00</v>
       </c>
       <c r="E581" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="582">
@@ -57770,16 +58267,16 @@
         <v>582</v>
       </c>
       <c r="B582" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C582">
-        <v>51</v>
+        <v>582</v>
       </c>
       <c r="D582" t="str">
         <v>T:2026-08-06|T:18:22:00</v>
       </c>
       <c r="E582" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="583">
@@ -57787,16 +58284,16 @@
         <v>583</v>
       </c>
       <c r="B583" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C583">
-        <v>52</v>
+        <v>583</v>
       </c>
       <c r="D583" t="str">
         <v>T:2026-08-06|T:20:27:00</v>
       </c>
       <c r="E583" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="584">
@@ -57804,16 +58301,16 @@
         <v>584</v>
       </c>
       <c r="B584" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C584">
-        <v>53</v>
+        <v>584</v>
       </c>
       <c r="D584" t="str">
         <v>T:2026-08-06|T:23:23:00</v>
       </c>
       <c r="E584" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="585">
@@ -57821,16 +58318,16 @@
         <v>585</v>
       </c>
       <c r="B585" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C585">
-        <v>55</v>
+        <v>585</v>
       </c>
       <c r="D585" t="str">
         <v>T:2026-08-07|T:07:19:00</v>
       </c>
       <c r="E585" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="586">
@@ -57838,16 +58335,16 @@
         <v>586</v>
       </c>
       <c r="B586" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C586">
-        <v>56</v>
+        <v>586</v>
       </c>
       <c r="D586" t="str">
         <v>T:2026-08-07|T:09:05:00</v>
       </c>
       <c r="E586" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="587">
@@ -57855,16 +58352,16 @@
         <v>587</v>
       </c>
       <c r="B587" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C587">
-        <v>57</v>
+        <v>587</v>
       </c>
       <c r="D587" t="str">
         <v>T:2026-08-07|T:10:54:00</v>
       </c>
       <c r="E587" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="588">
@@ -57872,16 +58369,16 @@
         <v>588</v>
       </c>
       <c r="B588" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C588">
-        <v>58</v>
+        <v>588</v>
       </c>
       <c r="D588" t="str">
         <v>T:2026-08-07|T:12:34:00</v>
       </c>
       <c r="E588" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="589">
@@ -57889,16 +58386,16 @@
         <v>589</v>
       </c>
       <c r="B589" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C589">
-        <v>59</v>
+        <v>589</v>
       </c>
       <c r="D589" t="str">
         <v>T:2026-08-07|T:15:35:00</v>
       </c>
       <c r="E589" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="590">
@@ -57906,16 +58403,16 @@
         <v>590</v>
       </c>
       <c r="B590" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C590">
-        <v>60</v>
+        <v>590</v>
       </c>
       <c r="D590" t="str">
         <v>T:2026-08-07|T:17:34:00</v>
       </c>
       <c r="E590" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="591">
@@ -57923,16 +58420,16 @@
         <v>591</v>
       </c>
       <c r="B591" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C591">
-        <v>61</v>
+        <v>591</v>
       </c>
       <c r="D591" t="str">
         <v>T:2026-08-07|T:18:46:00</v>
       </c>
       <c r="E591" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="592">
@@ -57940,16 +58437,16 @@
         <v>592</v>
       </c>
       <c r="B592" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C592">
-        <v>62</v>
+        <v>592</v>
       </c>
       <c r="D592" t="str">
         <v>T:2026-08-07|T:19:30:00</v>
       </c>
       <c r="E592" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="593">
@@ -57957,16 +58454,16 @@
         <v>593</v>
       </c>
       <c r="B593" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C593">
-        <v>63</v>
+        <v>593</v>
       </c>
       <c r="D593" t="str">
         <v>T:2026-08-07|T:21:38:00</v>
       </c>
       <c r="E593" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="594">
@@ -57974,16 +58471,16 @@
         <v>594</v>
       </c>
       <c r="B594" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C594">
-        <v>64</v>
+        <v>594</v>
       </c>
       <c r="D594" t="str">
         <v>T:2026-08-08|T:07:35:00</v>
       </c>
       <c r="E594" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="595">
@@ -57991,16 +58488,16 @@
         <v>595</v>
       </c>
       <c r="B595" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C595">
-        <v>65</v>
+        <v>595</v>
       </c>
       <c r="D595" t="str">
         <v>T:2026-08-08|T:09:40:00</v>
       </c>
       <c r="E595" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="596">
@@ -58008,16 +58505,16 @@
         <v>596</v>
       </c>
       <c r="B596" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C596">
-        <v>66</v>
+        <v>596</v>
       </c>
       <c r="D596" t="str">
         <v>T:2026-08-08|T:12:27:00</v>
       </c>
       <c r="E596" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="597">
@@ -58025,16 +58522,16 @@
         <v>597</v>
       </c>
       <c r="B597" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C597">
-        <v>67</v>
+        <v>597</v>
       </c>
       <c r="D597" t="str">
         <v>T:2026-08-08|T:13:32:00</v>
       </c>
       <c r="E597" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="598">
@@ -58042,16 +58539,16 @@
         <v>598</v>
       </c>
       <c r="B598" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C598">
-        <v>68</v>
+        <v>598</v>
       </c>
       <c r="D598" t="str">
         <v>T:2026-08-08|T:15:34:00</v>
       </c>
       <c r="E598" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="599">
@@ -58059,16 +58556,16 @@
         <v>599</v>
       </c>
       <c r="B599" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C599">
-        <v>69</v>
+        <v>599</v>
       </c>
       <c r="D599" t="str">
         <v>T:2026-08-08|T:17:23:00</v>
       </c>
       <c r="E599" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="600">
@@ -58076,16 +58573,16 @@
         <v>600</v>
       </c>
       <c r="B600" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C600">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="D600" t="str">
         <v>T:2026-08-08|T:18:55:00</v>
       </c>
       <c r="E600" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="601">
@@ -58093,16 +58590,16 @@
         <v>601</v>
       </c>
       <c r="B601" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C601">
-        <v>71</v>
+        <v>601</v>
       </c>
       <c r="D601" t="str">
         <v>T:2026-08-08|T:21:25:00</v>
       </c>
       <c r="E601" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="602">
@@ -58110,16 +58607,16 @@
         <v>602</v>
       </c>
       <c r="B602" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C602">
-        <v>72</v>
+        <v>602</v>
       </c>
       <c r="D602" t="str">
         <v>T:2026-08-08|T:23:46:00</v>
       </c>
       <c r="E602" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="603">
@@ -58127,16 +58624,16 @@
         <v>603</v>
       </c>
       <c r="B603" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C603">
-        <v>73</v>
+        <v>603</v>
       </c>
       <c r="D603" t="str">
         <v>T:2026-08-09|T:02:08:00</v>
       </c>
       <c r="E603" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="604">
@@ -58144,16 +58641,16 @@
         <v>604</v>
       </c>
       <c r="B604" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C604">
-        <v>74</v>
+        <v>604</v>
       </c>
       <c r="D604" t="str">
         <v>T:2026-08-09|T:04:20:00</v>
       </c>
       <c r="E604" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="605">
@@ -58161,16 +58658,16 @@
         <v>605</v>
       </c>
       <c r="B605" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C605">
-        <v>75</v>
+        <v>605</v>
       </c>
       <c r="D605" t="str">
         <v>T:2026-08-09|T:06:25:00</v>
       </c>
       <c r="E605" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="606">
@@ -58178,16 +58675,16 @@
         <v>606</v>
       </c>
       <c r="B606" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C606">
-        <v>76</v>
+        <v>606</v>
       </c>
       <c r="D606" t="str">
         <v>T:2026-08-09|T:07:40:00</v>
       </c>
       <c r="E606" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="607">
@@ -58195,16 +58692,16 @@
         <v>607</v>
       </c>
       <c r="B607" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C607">
-        <v>77</v>
+        <v>607</v>
       </c>
       <c r="D607" t="str">
         <v>T:2026-08-09|T:11:32:00</v>
       </c>
       <c r="E607" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="608">
@@ -58212,16 +58709,16 @@
         <v>608</v>
       </c>
       <c r="B608" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C608">
-        <v>78</v>
+        <v>608</v>
       </c>
       <c r="D608" t="str">
         <v>T:2026-08-09|T:13:36:00</v>
       </c>
       <c r="E608" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="609">
@@ -58229,16 +58726,16 @@
         <v>609</v>
       </c>
       <c r="B609" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C609">
-        <v>79</v>
+        <v>609</v>
       </c>
       <c r="D609" t="str">
         <v>T:2026-08-09|T:22:36:00</v>
       </c>
       <c r="E609" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="610">
@@ -58246,16 +58743,16 @@
         <v>610</v>
       </c>
       <c r="B610" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C610">
-        <v>80</v>
+        <v>610</v>
       </c>
       <c r="D610" t="str">
         <v>T:2026-08-10|T:00:37:00</v>
       </c>
       <c r="E610" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="611">
@@ -58263,16 +58760,16 @@
         <v>611</v>
       </c>
       <c r="B611" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C611">
-        <v>81</v>
+        <v>611</v>
       </c>
       <c r="D611" t="str">
         <v>T:2026-08-10|T:02:33:00</v>
       </c>
       <c r="E611" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="612">
@@ -58280,16 +58777,16 @@
         <v>612</v>
       </c>
       <c r="B612" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C612">
-        <v>82</v>
+        <v>612</v>
       </c>
       <c r="D612" t="str">
         <v>T:2026-08-10|T:04:32:00</v>
       </c>
       <c r="E612" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="613">
@@ -58297,16 +58794,16 @@
         <v>613</v>
       </c>
       <c r="B613" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C613">
-        <v>83</v>
+        <v>613</v>
       </c>
       <c r="D613" t="str">
         <v>T:2026-08-10|T:06:39:00</v>
       </c>
       <c r="E613" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="614">
@@ -58314,16 +58811,16 @@
         <v>614</v>
       </c>
       <c r="B614" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C614">
-        <v>84</v>
+        <v>614</v>
       </c>
       <c r="D614" t="str">
         <v>T:2026-08-10|T:10:43:00</v>
       </c>
       <c r="E614" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="615">
@@ -58331,16 +58828,16 @@
         <v>615</v>
       </c>
       <c r="B615" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C615">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="D615" t="str">
         <v>T:2026-08-10|T:12:52:00</v>
       </c>
       <c r="E615" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="616">
@@ -58348,16 +58845,16 @@
         <v>616</v>
       </c>
       <c r="B616" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C616">
-        <v>86</v>
+        <v>616</v>
       </c>
       <c r="D616" t="str">
         <v>T:2026-08-10|T:16:16:00</v>
       </c>
       <c r="E616" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="617">
@@ -58365,16 +58862,16 @@
         <v>617</v>
       </c>
       <c r="B617" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C617">
-        <v>87</v>
+        <v>617</v>
       </c>
       <c r="D617" t="str">
         <v>T:2026-08-10|T:17:18:00</v>
       </c>
       <c r="E617" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="618">
@@ -58382,16 +58879,16 @@
         <v>618</v>
       </c>
       <c r="B618" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C618">
-        <v>88</v>
+        <v>618</v>
       </c>
       <c r="D618" t="str">
         <v>T:2026-08-10|T:19:29:00</v>
       </c>
       <c r="E618" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="619">
@@ -58399,16 +58896,16 @@
         <v>619</v>
       </c>
       <c r="B619" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C619">
-        <v>89</v>
+        <v>619</v>
       </c>
       <c r="D619" t="str">
         <v>T:2026-08-11|T:00:34:00</v>
       </c>
       <c r="E619" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="620">
@@ -58416,16 +58913,16 @@
         <v>620</v>
       </c>
       <c r="B620" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C620">
-        <v>90</v>
+        <v>620</v>
       </c>
       <c r="D620" t="str">
         <v>T:2026-08-11|T:02:43:00</v>
       </c>
       <c r="E620" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="621">
@@ -58433,16 +58930,16 @@
         <v>621</v>
       </c>
       <c r="B621" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C621">
-        <v>91</v>
+        <v>621</v>
       </c>
       <c r="D621" t="str">
         <v>T:2026-08-11|T:04:30:00</v>
       </c>
       <c r="E621" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="622">
@@ -58450,16 +58947,16 @@
         <v>622</v>
       </c>
       <c r="B622" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C622">
-        <v>94</v>
+        <v>622</v>
       </c>
       <c r="D622" t="str">
         <v>T:2026-08-11|T:08:40:00</v>
       </c>
       <c r="E622" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="623">
@@ -58467,16 +58964,16 @@
         <v>623</v>
       </c>
       <c r="B623" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C623">
-        <v>92</v>
+        <v>623</v>
       </c>
       <c r="D623" t="str">
         <v>T:2026-08-11|T:10:59:00</v>
       </c>
       <c r="E623" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="624">
@@ -58484,16 +58981,16 @@
         <v>624</v>
       </c>
       <c r="B624" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C624">
-        <v>93</v>
+        <v>624</v>
       </c>
       <c r="D624" t="str">
         <v>T:2026-08-11|T:11:59:00</v>
       </c>
       <c r="E624" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="625">
@@ -58501,16 +58998,16 @@
         <v>625</v>
       </c>
       <c r="B625" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C625">
-        <v>95</v>
+        <v>625</v>
       </c>
       <c r="D625" t="str">
         <v>T:2026-08-11|T:16:23:00</v>
       </c>
       <c r="E625" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="626">
@@ -58518,16 +59015,16 @@
         <v>626</v>
       </c>
       <c r="B626" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C626">
-        <v>96</v>
+        <v>626</v>
       </c>
       <c r="D626" t="str">
         <v>T:2026-08-11|T:18:39:00</v>
       </c>
       <c r="E626" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="627">
@@ -58535,16 +59032,16 @@
         <v>627</v>
       </c>
       <c r="B627" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C627">
-        <v>97</v>
+        <v>627</v>
       </c>
       <c r="D627" t="str">
         <v>T:2026-08-11|T:20:02:00</v>
       </c>
       <c r="E627" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="628">
@@ -58552,16 +59049,16 @@
         <v>628</v>
       </c>
       <c r="B628" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C628">
-        <v>98</v>
+        <v>628</v>
       </c>
       <c r="D628" t="str">
         <v>T:2026-08-11|T:22:16:00</v>
       </c>
       <c r="E628" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="629">
@@ -58569,16 +59066,16 @@
         <v>629</v>
       </c>
       <c r="B629" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C629">
-        <v>99</v>
+        <v>629</v>
       </c>
       <c r="D629" t="str">
         <v>T:2026-08-12|T:00:19:00</v>
       </c>
       <c r="E629" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="630">
@@ -58586,16 +59083,16 @@
         <v>630</v>
       </c>
       <c r="B630" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C630">
-        <v>100</v>
+        <v>630</v>
       </c>
       <c r="D630" t="str">
         <v>T:2026-08-12|T:02:06:00</v>
       </c>
       <c r="E630" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="631">
@@ -58603,16 +59100,16 @@
         <v>631</v>
       </c>
       <c r="B631" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C631">
-        <v>101</v>
+        <v>631</v>
       </c>
       <c r="D631" t="str">
         <v>T:2026-08-12|T:04:09:00</v>
       </c>
       <c r="E631" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="632">
@@ -58620,16 +59117,16 @@
         <v>632</v>
       </c>
       <c r="B632" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C632">
-        <v>102</v>
+        <v>632</v>
       </c>
       <c r="D632" t="str">
         <v>T:2026-08-12|T:08:35:00</v>
       </c>
       <c r="E632" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="633">
@@ -58637,16 +59134,16 @@
         <v>633</v>
       </c>
       <c r="B633" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C633">
-        <v>103</v>
+        <v>633</v>
       </c>
       <c r="D633" t="str">
         <v>T:2026-08-12|T:13:39:00</v>
       </c>
       <c r="E633" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="634">
@@ -58654,16 +59151,16 @@
         <v>634</v>
       </c>
       <c r="B634" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C634">
-        <v>104</v>
+        <v>634</v>
       </c>
       <c r="D634" t="str">
         <v>T:2026-08-12|T:16:00:00</v>
       </c>
       <c r="E634" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="635">
@@ -58671,16 +59168,16 @@
         <v>635</v>
       </c>
       <c r="B635" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C635">
-        <v>105</v>
+        <v>635</v>
       </c>
       <c r="D635" t="str">
         <v>T:2026-08-12|T:21:04:00</v>
       </c>
       <c r="E635" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="636">
@@ -58688,16 +59185,16 @@
         <v>636</v>
       </c>
       <c r="B636" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C636">
-        <v>106</v>
+        <v>636</v>
       </c>
       <c r="D636" t="str">
         <v>T:2026-08-12|T:23:09:00</v>
       </c>
       <c r="E636" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="637">
@@ -58705,16 +59202,16 @@
         <v>637</v>
       </c>
       <c r="B637" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C637">
-        <v>107</v>
+        <v>637</v>
       </c>
       <c r="D637" t="str">
         <v>T:2026-08-13|T:01:16:00</v>
       </c>
       <c r="E637" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="638">
@@ -58722,16 +59219,16 @@
         <v>638</v>
       </c>
       <c r="B638" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C638">
-        <v>108</v>
+        <v>638</v>
       </c>
       <c r="D638" t="str">
         <v>T:2026-08-13|T:03:27:00</v>
       </c>
       <c r="E638" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="639">
@@ -58739,16 +59236,16 @@
         <v>639</v>
       </c>
       <c r="B639" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C639">
-        <v>109</v>
+        <v>639</v>
       </c>
       <c r="D639" t="str">
         <v>T:2026-08-13|T:06:58:00</v>
       </c>
       <c r="E639" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="640">
@@ -58756,16 +59253,16 @@
         <v>640</v>
       </c>
       <c r="B640" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C640">
-        <v>110</v>
+        <v>640</v>
       </c>
       <c r="D640" t="str">
         <v>T:2026-08-13|T:07:37:00</v>
       </c>
       <c r="E640" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="641">
@@ -58773,16 +59270,16 @@
         <v>641</v>
       </c>
       <c r="B641" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C641">
-        <v>111</v>
+        <v>641</v>
       </c>
       <c r="D641" t="str">
         <v>T:2026-08-13|T:09:29:00</v>
       </c>
       <c r="E641" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="642">
@@ -58790,16 +59287,16 @@
         <v>642</v>
       </c>
       <c r="B642" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C642">
-        <v>112</v>
+        <v>642</v>
       </c>
       <c r="D642" t="str">
         <v>T:2026-08-13|T:15:15:00</v>
       </c>
       <c r="E642" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="643">
@@ -58807,16 +59304,16 @@
         <v>643</v>
       </c>
       <c r="B643" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C643">
-        <v>113</v>
+        <v>643</v>
       </c>
       <c r="D643" t="str">
         <v>T:2026-08-13|T:17:30:00</v>
       </c>
       <c r="E643" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="644">
@@ -58824,16 +59321,16 @@
         <v>644</v>
       </c>
       <c r="B644" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C644">
-        <v>114</v>
+        <v>644</v>
       </c>
       <c r="D644" t="str">
         <v>T:2026-08-13|T:20:29:00</v>
       </c>
       <c r="E644" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="645">
@@ -58841,16 +59338,16 @@
         <v>645</v>
       </c>
       <c r="B645" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C645">
-        <v>115</v>
+        <v>645</v>
       </c>
       <c r="D645" t="str">
         <v>T:2026-08-13|T:22:40:00</v>
       </c>
       <c r="E645" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="646">
@@ -58858,16 +59355,16 @@
         <v>646</v>
       </c>
       <c r="B646" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C646">
-        <v>116</v>
+        <v>646</v>
       </c>
       <c r="D646" t="str">
         <v>T:2026-08-14|T:01:46:00</v>
       </c>
       <c r="E646" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="647">
@@ -58875,16 +59372,16 @@
         <v>647</v>
       </c>
       <c r="B647" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C647">
-        <v>117</v>
+        <v>647</v>
       </c>
       <c r="D647" t="str">
         <v>T:2026-08-14|T:03:50:00</v>
       </c>
       <c r="E647" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="648">
@@ -58892,16 +59389,16 @@
         <v>648</v>
       </c>
       <c r="B648" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C648">
-        <v>118</v>
+        <v>648</v>
       </c>
       <c r="D648" t="str">
         <v>T:2026-08-14|T:05:37:00</v>
       </c>
       <c r="E648" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="649">
@@ -58909,16 +59406,16 @@
         <v>649</v>
       </c>
       <c r="B649" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C649">
-        <v>119</v>
+        <v>649</v>
       </c>
       <c r="D649" t="str">
         <v>T:2026-08-14|T:06:44:00</v>
       </c>
       <c r="E649" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="650">
@@ -58926,16 +59423,16 @@
         <v>650</v>
       </c>
       <c r="B650" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C650">
-        <v>120</v>
+        <v>650</v>
       </c>
       <c r="D650" t="str">
         <v>T:2026-08-14|T:08:46:00</v>
       </c>
       <c r="E650" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="651">
@@ -58943,16 +59440,16 @@
         <v>651</v>
       </c>
       <c r="B651" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C651">
-        <v>121</v>
+        <v>651</v>
       </c>
       <c r="D651" t="str">
         <v>T:2026-08-14|T:12:41:00</v>
       </c>
       <c r="E651" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="652">
@@ -58960,16 +59457,16 @@
         <v>652</v>
       </c>
       <c r="B652" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C652">
-        <v>122</v>
+        <v>652</v>
       </c>
       <c r="D652" t="str">
         <v>T:2026-08-14|T:15:21:00</v>
       </c>
       <c r="E652" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="653">
@@ -58977,16 +59474,16 @@
         <v>653</v>
       </c>
       <c r="B653" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C653">
-        <v>123</v>
+        <v>653</v>
       </c>
       <c r="D653" t="str">
         <v>T:2026-08-14|T:17:19:00</v>
       </c>
       <c r="E653" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="654">
@@ -58994,16 +59491,16 @@
         <v>654</v>
       </c>
       <c r="B654" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C654">
-        <v>124</v>
+        <v>654</v>
       </c>
       <c r="D654" t="str">
         <v>T:2026-08-14|T:20:57:00</v>
       </c>
       <c r="E654" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="655">
@@ -59011,16 +59508,16 @@
         <v>655</v>
       </c>
       <c r="B655" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C655">
-        <v>125</v>
+        <v>655</v>
       </c>
       <c r="D655" t="str">
         <v>T:2026-08-14|T:22:45:00</v>
       </c>
       <c r="E655" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="656">
@@ -59028,16 +59525,16 @@
         <v>656</v>
       </c>
       <c r="B656" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C656">
-        <v>126</v>
+        <v>656</v>
       </c>
       <c r="D656" t="str">
         <v>T:2026-08-15|T:01:01:00</v>
       </c>
       <c r="E656" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="657">
@@ -59045,16 +59542,16 @@
         <v>657</v>
       </c>
       <c r="B657" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C657">
-        <v>127</v>
+        <v>657</v>
       </c>
       <c r="D657" t="str">
         <v>T:2026-08-15|T:03:00:00</v>
       </c>
       <c r="E657" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="658">
@@ -59062,16 +59559,16 @@
         <v>658</v>
       </c>
       <c r="B658" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C658">
-        <v>128</v>
+        <v>658</v>
       </c>
       <c r="D658" t="str">
         <v>T:2026-08-15|T:04:40:00</v>
       </c>
       <c r="E658" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="659">
@@ -59079,16 +59576,16 @@
         <v>659</v>
       </c>
       <c r="B659" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C659">
-        <v>129</v>
+        <v>659</v>
       </c>
       <c r="D659" t="str">
         <v>T:2026-08-15|T:06:44:00</v>
       </c>
       <c r="E659" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="660">
@@ -59096,16 +59593,16 @@
         <v>660</v>
       </c>
       <c r="B660" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C660">
-        <v>130</v>
+        <v>660</v>
       </c>
       <c r="D660" t="str">
         <v>T:2026-08-15|T:08:42:00</v>
       </c>
       <c r="E660" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="661">
@@ -59113,16 +59610,16 @@
         <v>661</v>
       </c>
       <c r="B661" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C661">
-        <v>131</v>
+        <v>661</v>
       </c>
       <c r="D661" t="str">
         <v>T:2026-08-15|T:11:53:00</v>
       </c>
       <c r="E661" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="662">
@@ -59130,16 +59627,16 @@
         <v>662</v>
       </c>
       <c r="B662" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C662">
-        <v>140</v>
+        <v>662</v>
       </c>
       <c r="D662" t="str">
         <v>T:2026-08-15|T:15:34:00</v>
       </c>
       <c r="E662" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="663">
@@ -59147,16 +59644,16 @@
         <v>663</v>
       </c>
       <c r="B663" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C663">
-        <v>132</v>
+        <v>663</v>
       </c>
       <c r="D663" t="str">
         <v>T:2026-08-15|T:15:41:00</v>
       </c>
       <c r="E663" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="664">
@@ -59164,16 +59661,16 @@
         <v>664</v>
       </c>
       <c r="B664" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C664">
-        <v>141</v>
+        <v>664</v>
       </c>
       <c r="D664" t="str">
         <v>T:2026-08-15|T:17:10:00</v>
       </c>
       <c r="E664" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="665">
@@ -59181,16 +59678,16 @@
         <v>665</v>
       </c>
       <c r="B665" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C665">
-        <v>133</v>
+        <v>665</v>
       </c>
       <c r="D665" t="str">
         <v>T:2026-08-15|T:20:19:00</v>
       </c>
       <c r="E665" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="666">
@@ -59198,16 +59695,16 @@
         <v>666</v>
       </c>
       <c r="B666" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C666">
-        <v>134</v>
+        <v>666</v>
       </c>
       <c r="D666" t="str">
         <v>T:2026-08-15|T:23:10:00</v>
       </c>
       <c r="E666" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="667">
@@ -59215,16 +59712,16 @@
         <v>667</v>
       </c>
       <c r="B667" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C667">
-        <v>135</v>
+        <v>667</v>
       </c>
       <c r="D667" t="str">
         <v>T:2026-08-16|T:01:25:00</v>
       </c>
       <c r="E667" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="668">
@@ -59232,16 +59729,16 @@
         <v>668</v>
       </c>
       <c r="B668" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C668">
-        <v>136</v>
+        <v>668</v>
       </c>
       <c r="D668" t="str">
         <v>T:2026-08-16|T:04:00:00</v>
       </c>
       <c r="E668" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="669">
@@ -59249,16 +59746,16 @@
         <v>669</v>
       </c>
       <c r="B669" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C669">
-        <v>137</v>
+        <v>669</v>
       </c>
       <c r="D669" t="str">
         <v>T:2026-08-16|T:07:06:00</v>
       </c>
       <c r="E669" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="670">
@@ -59266,16 +59763,16 @@
         <v>670</v>
       </c>
       <c r="B670" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C670">
-        <v>138</v>
+        <v>670</v>
       </c>
       <c r="D670" t="str">
         <v>T:2026-08-16|T:09:38:00</v>
       </c>
       <c r="E670" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="671">
@@ -59283,16 +59780,16 @@
         <v>671</v>
       </c>
       <c r="B671" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C671">
-        <v>139</v>
+        <v>671</v>
       </c>
       <c r="D671" t="str">
         <v>T:2026-08-16|T:12:52:00</v>
       </c>
       <c r="E671" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="672">
@@ -59300,16 +59797,16 @@
         <v>672</v>
       </c>
       <c r="B672" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C672">
-        <v>142</v>
+        <v>672</v>
       </c>
       <c r="D672" t="str">
         <v>T:2026-08-17|T:00:22:00</v>
       </c>
       <c r="E672" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="673">
@@ -59317,16 +59814,16 @@
         <v>673</v>
       </c>
       <c r="B673" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C673">
-        <v>143</v>
+        <v>673</v>
       </c>
       <c r="D673" t="str">
         <v>T:2026-08-17|T:03:15:00</v>
       </c>
       <c r="E673" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="674">
@@ -59334,16 +59831,16 @@
         <v>674</v>
       </c>
       <c r="B674" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C674">
-        <v>144</v>
+        <v>674</v>
       </c>
       <c r="D674" t="str">
         <v>T:2026-08-17|T:05:20:00</v>
       </c>
       <c r="E674" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="675">
@@ -59351,16 +59848,16 @@
         <v>675</v>
       </c>
       <c r="B675" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C675">
-        <v>145</v>
+        <v>675</v>
       </c>
       <c r="D675" t="str">
         <v>T:2026-08-17|T:08:10:00</v>
       </c>
       <c r="E675" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="676">
@@ -59368,16 +59865,16 @@
         <v>676</v>
       </c>
       <c r="B676" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C676">
-        <v>146</v>
+        <v>676</v>
       </c>
       <c r="D676" t="str">
         <v>T:2026-08-17|T:09:53:00</v>
       </c>
       <c r="E676" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="677">
@@ -59385,16 +59882,16 @@
         <v>677</v>
       </c>
       <c r="B677" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C677">
-        <v>147</v>
+        <v>677</v>
       </c>
       <c r="D677" t="str">
         <v>T:2026-08-17|T:12:59:00</v>
       </c>
       <c r="E677" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="678">
@@ -59402,16 +59899,16 @@
         <v>678</v>
       </c>
       <c r="B678" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C678">
-        <v>148</v>
+        <v>678</v>
       </c>
       <c r="D678" t="str">
         <v>T:2026-08-17|T:15:00:00</v>
       </c>
       <c r="E678" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="679">
@@ -59419,16 +59916,16 @@
         <v>679</v>
       </c>
       <c r="B679" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C679">
-        <v>149</v>
+        <v>679</v>
       </c>
       <c r="D679" t="str">
         <v>T:2026-08-17|T:17:30:00</v>
       </c>
       <c r="E679" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="680">
@@ -59436,16 +59933,16 @@
         <v>680</v>
       </c>
       <c r="B680" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C680">
-        <v>150</v>
+        <v>680</v>
       </c>
       <c r="D680" t="str">
         <v>T:2026-08-17|T:19:15:00</v>
       </c>
       <c r="E680" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="681">
@@ -59453,16 +59950,16 @@
         <v>681</v>
       </c>
       <c r="B681" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C681">
-        <v>151</v>
+        <v>681</v>
       </c>
       <c r="D681" t="str">
         <v>T:2026-08-17|T:21:50:00</v>
       </c>
       <c r="E681" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="682">
@@ -59470,16 +59967,16 @@
         <v>682</v>
       </c>
       <c r="B682" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C682">
-        <v>152</v>
+        <v>682</v>
       </c>
       <c r="D682" t="str">
         <v>T:2026-08-18|T:00:03:00</v>
       </c>
       <c r="E682" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="683">
@@ -59487,16 +59984,16 @@
         <v>683</v>
       </c>
       <c r="B683" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C683">
-        <v>153</v>
+        <v>683</v>
       </c>
       <c r="D683" t="str">
         <v>T:2026-08-18|T:03:13:00</v>
       </c>
       <c r="E683" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="684">
@@ -59504,16 +60001,16 @@
         <v>684</v>
       </c>
       <c r="B684" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C684">
-        <v>154</v>
+        <v>684</v>
       </c>
       <c r="D684" t="str">
         <v>T:2026-08-18|T:05:19:00</v>
       </c>
       <c r="E684" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="685">
@@ -59521,16 +60018,16 @@
         <v>685</v>
       </c>
       <c r="B685" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C685">
-        <v>155</v>
+        <v>685</v>
       </c>
       <c r="D685" t="str">
         <v>T:2026-08-18|T:08:33:00</v>
       </c>
       <c r="E685" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="686">
@@ -59538,16 +60035,16 @@
         <v>686</v>
       </c>
       <c r="B686" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C686">
-        <v>156</v>
+        <v>686</v>
       </c>
       <c r="D686" t="str">
         <v>T:2026-08-18|T:15:40:00</v>
       </c>
       <c r="E686" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="687">
@@ -59555,16 +60052,16 @@
         <v>687</v>
       </c>
       <c r="B687" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C687">
-        <v>157</v>
+        <v>687</v>
       </c>
       <c r="D687" t="str">
         <v>T:2026-08-18|T:20:00:00</v>
       </c>
       <c r="E687" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="688">
@@ -59572,16 +60069,16 @@
         <v>688</v>
       </c>
       <c r="B688" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C688">
-        <v>158</v>
+        <v>688</v>
       </c>
       <c r="D688" t="str">
         <v>T:2026-08-18|T:21:30:00</v>
       </c>
       <c r="E688" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="689">
@@ -59589,16 +60086,16 @@
         <v>689</v>
       </c>
       <c r="B689" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C689">
-        <v>159</v>
+        <v>689</v>
       </c>
       <c r="D689" t="str">
         <v>T:2026-08-18|T:23:34:00</v>
       </c>
       <c r="E689" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="690">
@@ -59606,16 +60103,16 @@
         <v>690</v>
       </c>
       <c r="B690" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C690">
-        <v>168</v>
+        <v>690</v>
       </c>
       <c r="D690" t="str">
         <v>T:2026-08-19|T:00:11:00</v>
       </c>
       <c r="E690" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="691">
@@ -59623,16 +60120,16 @@
         <v>691</v>
       </c>
       <c r="B691" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C691">
-        <v>160</v>
+        <v>691</v>
       </c>
       <c r="D691" t="str">
         <v>T:2026-08-19|T:03:11:00</v>
       </c>
       <c r="E691" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="692">
@@ -59640,16 +60137,16 @@
         <v>692</v>
       </c>
       <c r="B692" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C692">
-        <v>161</v>
+        <v>692</v>
       </c>
       <c r="D692" t="str">
         <v>T:2026-08-19|T:05:11:00</v>
       </c>
       <c r="E692" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="693">
@@ -59657,16 +60154,16 @@
         <v>693</v>
       </c>
       <c r="B693" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C693">
-        <v>162</v>
+        <v>693</v>
       </c>
       <c r="D693" t="str">
         <v>T:2026-08-19|T:06:20:00</v>
       </c>
       <c r="E693" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="694">
@@ -59674,16 +60171,16 @@
         <v>694</v>
       </c>
       <c r="B694" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C694">
-        <v>163</v>
+        <v>694</v>
       </c>
       <c r="D694" t="str">
         <v>T:2026-08-19|T:08:20:00</v>
       </c>
       <c r="E694" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="695">
@@ -59691,16 +60188,16 @@
         <v>695</v>
       </c>
       <c r="B695" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C695">
-        <v>164</v>
+        <v>695</v>
       </c>
       <c r="D695" t="str">
         <v>T:2026-08-19|T:11:44:00</v>
       </c>
       <c r="E695" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="696">
@@ -59708,16 +60205,16 @@
         <v>696</v>
       </c>
       <c r="B696" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C696">
-        <v>165</v>
+        <v>696</v>
       </c>
       <c r="D696" t="str">
         <v>T:2026-08-19|T:13:19:00</v>
       </c>
       <c r="E696" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="697">
@@ -59725,16 +60222,16 @@
         <v>697</v>
       </c>
       <c r="B697" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C697">
-        <v>166</v>
+        <v>697</v>
       </c>
       <c r="D697" t="str">
         <v>T:2026-08-19|T:21:45:00</v>
       </c>
       <c r="E697" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="698">
@@ -59742,16 +60239,16 @@
         <v>698</v>
       </c>
       <c r="B698" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C698">
-        <v>167</v>
+        <v>698</v>
       </c>
       <c r="D698" t="str">
         <v>T:2026-08-19|T:22:37:00</v>
       </c>
       <c r="E698" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="699">
@@ -59759,16 +60256,16 @@
         <v>699</v>
       </c>
       <c r="B699" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C699">
-        <v>169</v>
+        <v>699</v>
       </c>
       <c r="D699" t="str">
         <v>T:2026-08-20|T:01:42:00</v>
       </c>
       <c r="E699" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="700">
@@ -59776,16 +60273,16 @@
         <v>700</v>
       </c>
       <c r="B700" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C700">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="D700" t="str">
         <v>T:2026-08-20|T:04:51:00</v>
       </c>
       <c r="E700" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="701">
@@ -59793,16 +60290,16 @@
         <v>701</v>
       </c>
       <c r="B701" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C701">
-        <v>171</v>
+        <v>701</v>
       </c>
       <c r="D701" t="str">
         <v>T:2026-08-20|T:08:15:00</v>
       </c>
       <c r="E701" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="702">
@@ -59810,16 +60307,16 @@
         <v>702</v>
       </c>
       <c r="B702" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C702">
-        <v>172</v>
+        <v>702</v>
       </c>
       <c r="D702" t="str">
         <v>T:2026-08-20|T:10:30:00</v>
       </c>
       <c r="E702" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="703">
@@ -59827,16 +60324,16 @@
         <v>703</v>
       </c>
       <c r="B703" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C703">
-        <v>173</v>
+        <v>703</v>
       </c>
       <c r="D703" t="str">
         <v>T:2026-08-20|T:13:24:00</v>
       </c>
       <c r="E703" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="704">
@@ -59844,16 +60341,16 @@
         <v>704</v>
       </c>
       <c r="B704" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C704">
-        <v>174</v>
+        <v>704</v>
       </c>
       <c r="D704" t="str">
         <v>T:2026-08-20|T:16:00:00</v>
       </c>
       <c r="E704" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="705">
@@ -59861,16 +60358,16 @@
         <v>705</v>
       </c>
       <c r="B705" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C705">
-        <v>175</v>
+        <v>705</v>
       </c>
       <c r="D705" t="str">
         <v>T:2026-08-20|T:21:00:00</v>
       </c>
       <c r="E705" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="706">
@@ -59878,16 +60375,16 @@
         <v>706</v>
       </c>
       <c r="B706" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C706">
-        <v>176</v>
+        <v>706</v>
       </c>
       <c r="D706" t="str">
         <v>T:2026-08-20|T:23:31:00</v>
       </c>
       <c r="E706" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="707">
@@ -59895,16 +60392,16 @@
         <v>707</v>
       </c>
       <c r="B707" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C707">
-        <v>177</v>
+        <v>707</v>
       </c>
       <c r="D707" t="str">
         <v>T:2026-08-21|T:07:46:00</v>
       </c>
       <c r="E707" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="708">
@@ -59912,16 +60409,16 @@
         <v>708</v>
       </c>
       <c r="B708" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C708">
-        <v>178</v>
+        <v>708</v>
       </c>
       <c r="D708" t="str">
         <v>T:2026-08-21|T:10:22:00</v>
       </c>
       <c r="E708" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="709">
@@ -59929,16 +60426,16 @@
         <v>709</v>
       </c>
       <c r="B709" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C709">
-        <v>179</v>
+        <v>709</v>
       </c>
       <c r="D709" t="str">
         <v>T:2026-08-21|T:13:20:00</v>
       </c>
       <c r="E709" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="710">
@@ -59946,16 +60443,16 @@
         <v>710</v>
       </c>
       <c r="B710" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C710">
-        <v>180</v>
+        <v>710</v>
       </c>
       <c r="D710" t="str">
         <v>T:2026-08-21|T:14:10:00</v>
       </c>
       <c r="E710" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="711">
@@ -59963,16 +60460,16 @@
         <v>711</v>
       </c>
       <c r="B711" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C711">
-        <v>181</v>
+        <v>711</v>
       </c>
       <c r="D711" t="str">
         <v>T:2026-08-21|T:19:30:00</v>
       </c>
       <c r="E711" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="712">
@@ -59980,16 +60477,16 @@
         <v>712</v>
       </c>
       <c r="B712" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C712">
-        <v>182</v>
+        <v>712</v>
       </c>
       <c r="D712" t="str">
         <v>T:2026-08-21|T:23:20:00</v>
       </c>
       <c r="E712" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="713">
@@ -59997,16 +60494,16 @@
         <v>713</v>
       </c>
       <c r="B713" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C713">
-        <v>183</v>
+        <v>713</v>
       </c>
       <c r="D713" t="str">
         <v>T:2026-08-22|T:01:22:00</v>
       </c>
       <c r="E713" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="714">
@@ -60014,16 +60511,16 @@
         <v>714</v>
       </c>
       <c r="B714" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C714">
-        <v>184</v>
+        <v>714</v>
       </c>
       <c r="D714" t="str">
         <v>T:2026-08-22|T:05:28:00</v>
       </c>
       <c r="E714" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="715">
@@ -60031,16 +60528,16 @@
         <v>715</v>
       </c>
       <c r="B715" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C715">
-        <v>186</v>
+        <v>715</v>
       </c>
       <c r="D715" t="str">
         <v>T:2026-08-22|T:11:30:00</v>
       </c>
       <c r="E715" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="716">
@@ -60048,16 +60545,16 @@
         <v>716</v>
       </c>
       <c r="B716" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C716">
-        <v>187</v>
+        <v>716</v>
       </c>
       <c r="D716" t="str">
         <v>T:2026-08-22|T:19:52:00</v>
       </c>
       <c r="E716" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="717">
@@ -60065,16 +60562,16 @@
         <v>717</v>
       </c>
       <c r="B717" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C717">
-        <v>185</v>
+        <v>717</v>
       </c>
       <c r="D717" t="str">
         <v>T:2026-08-22|T:23:30:00</v>
       </c>
       <c r="E717" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="718">
@@ -60082,16 +60579,16 @@
         <v>718</v>
       </c>
       <c r="B718" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C718">
-        <v>188</v>
+        <v>718</v>
       </c>
       <c r="D718" t="str">
         <v>T:2026-08-22|T:23:36:00</v>
       </c>
       <c r="E718" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="719">
@@ -60099,16 +60596,16 @@
         <v>719</v>
       </c>
       <c r="B719" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C719">
-        <v>189</v>
+        <v>719</v>
       </c>
       <c r="D719" t="str">
         <v>T:2026-08-23|T:01:37:00</v>
       </c>
       <c r="E719" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="720">
@@ -60116,16 +60613,16 @@
         <v>720</v>
       </c>
       <c r="B720" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C720">
-        <v>190</v>
+        <v>720</v>
       </c>
       <c r="D720" t="str">
         <v>T:2026-08-23|T:03:25:00</v>
       </c>
       <c r="E720" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="721">
@@ -60133,16 +60630,16 @@
         <v>721</v>
       </c>
       <c r="B721" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C721">
-        <v>191</v>
+        <v>721</v>
       </c>
       <c r="D721" t="str">
         <v>T:2026-08-23|T:05:29:00</v>
       </c>
       <c r="E721" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="722">
@@ -60150,16 +60647,16 @@
         <v>722</v>
       </c>
       <c r="B722" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C722">
-        <v>192</v>
+        <v>722</v>
       </c>
       <c r="D722" t="str">
         <v>T:2026-08-23|T:06:50:00</v>
       </c>
       <c r="E722" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="723">
@@ -60167,16 +60664,16 @@
         <v>723</v>
       </c>
       <c r="B723" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C723">
-        <v>193</v>
+        <v>723</v>
       </c>
       <c r="D723" t="str">
         <v>T:2026-08-23|T:09:10:00</v>
       </c>
       <c r="E723" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="724">
@@ -60184,16 +60681,16 @@
         <v>724</v>
       </c>
       <c r="B724" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C724">
-        <v>194</v>
+        <v>724</v>
       </c>
       <c r="D724" t="str">
         <v>T:2026-08-23|T:11:20:00</v>
       </c>
       <c r="E724" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="725">
@@ -60201,16 +60698,16 @@
         <v>725</v>
       </c>
       <c r="B725" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C725">
-        <v>195</v>
+        <v>725</v>
       </c>
       <c r="D725" t="str">
         <v>T:2026-08-23|T:13:30:00</v>
       </c>
       <c r="E725" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="726">
@@ -60218,16 +60715,16 @@
         <v>726</v>
       </c>
       <c r="B726" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C726">
-        <v>196</v>
+        <v>726</v>
       </c>
       <c r="D726" t="str">
         <v>T:2026-08-23|T:22:50:00</v>
       </c>
       <c r="E726" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="727">
@@ -60235,16 +60732,16 @@
         <v>727</v>
       </c>
       <c r="B727" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C727">
-        <v>197</v>
+        <v>727</v>
       </c>
       <c r="D727" t="str">
         <v>T:2026-08-24|T:03:11:00</v>
       </c>
       <c r="E727" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="728">
@@ -60252,16 +60749,16 @@
         <v>728</v>
       </c>
       <c r="B728" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C728">
-        <v>198</v>
+        <v>728</v>
       </c>
       <c r="D728" t="str">
         <v>T:2026-08-24|T:05:30:00</v>
       </c>
       <c r="E728" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="729">
@@ -60269,16 +60766,16 @@
         <v>729</v>
       </c>
       <c r="B729" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C729">
-        <v>200</v>
+        <v>729</v>
       </c>
       <c r="D729" t="str">
         <v>T:2026-08-24|T:08:20:00</v>
       </c>
       <c r="E729" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="730">
@@ -60286,16 +60783,16 @@
         <v>730</v>
       </c>
       <c r="B730" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C730">
-        <v>201</v>
+        <v>730</v>
       </c>
       <c r="D730" t="str">
         <v>T:2026-08-24|T:10:40:00</v>
       </c>
       <c r="E730" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="731">
@@ -60303,16 +60800,16 @@
         <v>731</v>
       </c>
       <c r="B731" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C731">
-        <v>202</v>
+        <v>731</v>
       </c>
       <c r="D731" t="str">
         <v>T:2026-08-24|T:12:45:00</v>
       </c>
       <c r="E731" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="732">
@@ -60320,16 +60817,16 @@
         <v>732</v>
       </c>
       <c r="B732" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C732">
-        <v>203</v>
+        <v>732</v>
       </c>
       <c r="D732" t="str">
         <v>T:2026-08-24|T:14:55:00</v>
       </c>
       <c r="E732" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="733">
@@ -60337,16 +60834,16 @@
         <v>733</v>
       </c>
       <c r="B733" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C733">
-        <v>204</v>
+        <v>733</v>
       </c>
       <c r="D733" t="str">
         <v>T:2026-08-24|T:17:00:00</v>
       </c>
       <c r="E733" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="734">
@@ -60354,16 +60851,16 @@
         <v>734</v>
       </c>
       <c r="B734" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C734">
-        <v>205</v>
+        <v>734</v>
       </c>
       <c r="D734" t="str">
         <v>T:2026-08-24|T:18:30:00</v>
       </c>
       <c r="E734" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="735">
@@ -60371,16 +60868,16 @@
         <v>735</v>
       </c>
       <c r="B735" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C735">
-        <v>206</v>
+        <v>735</v>
       </c>
       <c r="D735" t="str">
         <v>T:2026-08-24|T:20:00:00</v>
       </c>
       <c r="E735" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="736">
@@ -60388,16 +60885,16 @@
         <v>736</v>
       </c>
       <c r="B736" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C736">
-        <v>199</v>
+        <v>736</v>
       </c>
       <c r="D736" t="str">
         <v>T:2026-08-24|T:20:20:00</v>
       </c>
       <c r="E736" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="737">
@@ -60405,16 +60902,16 @@
         <v>737</v>
       </c>
       <c r="B737" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C737">
-        <v>207</v>
+        <v>737</v>
       </c>
       <c r="D737" t="str">
         <v>T:2026-08-24|T:23:08:00</v>
       </c>
       <c r="E737" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="738">
@@ -60422,16 +60919,16 @@
         <v>738</v>
       </c>
       <c r="B738" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C738">
-        <v>208</v>
+        <v>738</v>
       </c>
       <c r="D738" t="str">
         <v>T:2026-08-25|T:01:05:00</v>
       </c>
       <c r="E738" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="739">
@@ -60439,16 +60936,16 @@
         <v>739</v>
       </c>
       <c r="B739" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C739">
-        <v>209</v>
+        <v>739</v>
       </c>
       <c r="D739" t="str">
         <v>T:2026-08-25|T:02:52:00</v>
       </c>
       <c r="E739" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="740">
@@ -60456,16 +60953,16 @@
         <v>740</v>
       </c>
       <c r="B740" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C740">
-        <v>210</v>
+        <v>740</v>
       </c>
       <c r="D740" t="str">
         <v>T:2026-08-25|T:05:06:00</v>
       </c>
       <c r="E740" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="741">
@@ -60473,16 +60970,16 @@
         <v>741</v>
       </c>
       <c r="B741" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C741">
-        <v>211</v>
+        <v>741</v>
       </c>
       <c r="D741" t="str">
         <v>T:2026-08-25|T:06:29:00</v>
       </c>
       <c r="E741" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="742">
@@ -60490,16 +60987,16 @@
         <v>742</v>
       </c>
       <c r="B742" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C742">
-        <v>212</v>
+        <v>742</v>
       </c>
       <c r="D742" t="str">
         <v>T:2026-08-25|T:08:20:00</v>
       </c>
       <c r="E742" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="743">
@@ -60507,16 +61004,16 @@
         <v>743</v>
       </c>
       <c r="B743" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C743">
-        <v>213</v>
+        <v>743</v>
       </c>
       <c r="D743" t="str">
         <v>T:2026-08-25|T:12:55:00</v>
       </c>
       <c r="E743" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="744">
@@ -60524,16 +61021,16 @@
         <v>744</v>
       </c>
       <c r="B744" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C744">
-        <v>214</v>
+        <v>744</v>
       </c>
       <c r="D744" t="str">
         <v>T:2026-08-25|T:15:40:00</v>
       </c>
       <c r="E744" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="745">
@@ -60541,16 +61038,16 @@
         <v>745</v>
       </c>
       <c r="B745" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C745">
-        <v>215</v>
+        <v>745</v>
       </c>
       <c r="D745" t="str">
         <v>T:2026-08-25|T:17:30:00</v>
       </c>
       <c r="E745" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="746">
@@ -60558,16 +61055,16 @@
         <v>746</v>
       </c>
       <c r="B746" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C746">
-        <v>216</v>
+        <v>746</v>
       </c>
       <c r="D746" t="str">
         <v>T:2026-08-25|T:19:10:00</v>
       </c>
       <c r="E746" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="747">
@@ -60575,16 +61072,16 @@
         <v>747</v>
       </c>
       <c r="B747" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C747">
-        <v>218</v>
+        <v>747</v>
       </c>
       <c r="D747" t="str">
         <v>T:2026-08-26|T:01:57:00</v>
       </c>
       <c r="E747" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="748">
@@ -60592,16 +61089,16 @@
         <v>748</v>
       </c>
       <c r="B748" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C748">
-        <v>219</v>
+        <v>748</v>
       </c>
       <c r="D748" t="str">
         <v>T:2026-08-26|T:05:17:00</v>
       </c>
       <c r="E748" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="749">
@@ -60609,16 +61106,16 @@
         <v>749</v>
       </c>
       <c r="B749" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C749">
-        <v>220</v>
+        <v>749</v>
       </c>
       <c r="D749" t="str">
         <v>T:2026-08-26|T:12:30:00</v>
       </c>
       <c r="E749" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="750">
@@ -60626,16 +61123,16 @@
         <v>750</v>
       </c>
       <c r="B750" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C750">
-        <v>221</v>
+        <v>750</v>
       </c>
       <c r="D750" t="str">
         <v>T:2026-08-26|T:16:08:00</v>
       </c>
       <c r="E750" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="751">
@@ -60643,16 +61140,16 @@
         <v>751</v>
       </c>
       <c r="B751" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C751">
-        <v>222</v>
+        <v>751</v>
       </c>
       <c r="D751" t="str">
         <v>T:2026-08-26|T:18:38:00</v>
       </c>
       <c r="E751" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="752">
@@ -60660,16 +61157,16 @@
         <v>752</v>
       </c>
       <c r="B752" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C752">
-        <v>223</v>
+        <v>752</v>
       </c>
       <c r="D752" t="str">
         <v>T:2026-08-26|T:20:30:00</v>
       </c>
       <c r="E752" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="753">
@@ -60677,16 +61174,16 @@
         <v>753</v>
       </c>
       <c r="B753" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C753">
-        <v>217</v>
+        <v>753</v>
       </c>
       <c r="D753" t="str">
         <v>T:2026-08-26|T:23:10:00</v>
       </c>
       <c r="E753" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="754">
@@ -60694,16 +61191,16 @@
         <v>754</v>
       </c>
       <c r="B754" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C754">
-        <v>224</v>
+        <v>754</v>
       </c>
       <c r="D754" t="str">
         <v>T:2026-08-26|T:23:26:00</v>
       </c>
       <c r="E754" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="755">
@@ -60711,16 +61208,16 @@
         <v>755</v>
       </c>
       <c r="B755" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C755">
-        <v>225</v>
+        <v>755</v>
       </c>
       <c r="D755" t="str">
         <v>T:2026-08-27|T:02:46:00</v>
       </c>
       <c r="E755" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="756">
@@ -60728,16 +61225,16 @@
         <v>756</v>
       </c>
       <c r="B756" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C756">
-        <v>226</v>
+        <v>756</v>
       </c>
       <c r="D756" t="str">
         <v>T:2026-08-27|T:05:04:00</v>
       </c>
       <c r="E756" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="757">
@@ -60745,16 +61242,16 @@
         <v>757</v>
       </c>
       <c r="B757" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C757">
-        <v>227</v>
+        <v>757</v>
       </c>
       <c r="D757" t="str">
         <v>T:2026-08-27|T:11:24:00</v>
       </c>
       <c r="E757" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="758">
@@ -60762,16 +61259,16 @@
         <v>758</v>
       </c>
       <c r="B758" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C758">
-        <v>228</v>
+        <v>758</v>
       </c>
       <c r="D758" t="str">
         <v>T:2026-08-27|T:12:43:00</v>
       </c>
       <c r="E758" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="759">
@@ -60779,16 +61276,16 @@
         <v>759</v>
       </c>
       <c r="B759" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C759">
-        <v>229</v>
+        <v>759</v>
       </c>
       <c r="D759" t="str">
         <v>T:2026-08-27|T:15:56:00</v>
       </c>
       <c r="E759" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="760">
@@ -60796,16 +61293,16 @@
         <v>760</v>
       </c>
       <c r="B760" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C760">
-        <v>230</v>
+        <v>760</v>
       </c>
       <c r="D760" t="str">
         <v>T:2026-08-27|T:17:50:00</v>
       </c>
       <c r="E760" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="761">
@@ -60813,16 +61310,16 @@
         <v>761</v>
       </c>
       <c r="B761" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C761">
-        <v>231</v>
+        <v>761</v>
       </c>
       <c r="D761" t="str">
         <v>T:2026-08-27|T:19:10:00</v>
       </c>
       <c r="E761" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="762">
@@ -60830,16 +61327,16 @@
         <v>762</v>
       </c>
       <c r="B762" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C762">
-        <v>232</v>
+        <v>762</v>
       </c>
       <c r="D762" t="str">
         <v>T:2026-08-27|T:23:05:00</v>
       </c>
       <c r="E762" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="763">
@@ -60847,16 +61344,16 @@
         <v>763</v>
       </c>
       <c r="B763" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C763">
-        <v>233</v>
+        <v>763</v>
       </c>
       <c r="D763" t="str">
         <v>T:2026-08-28|T:03:00:00</v>
       </c>
       <c r="E763" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="764">
@@ -60864,16 +61361,16 @@
         <v>764</v>
       </c>
       <c r="B764" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C764">
-        <v>234</v>
+        <v>764</v>
       </c>
       <c r="D764" t="str">
         <v>T:2026-08-28|T:05:15:00</v>
       </c>
       <c r="E764" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="765">
@@ -60881,16 +61378,16 @@
         <v>765</v>
       </c>
       <c r="B765" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C765">
-        <v>235</v>
+        <v>765</v>
       </c>
       <c r="D765" t="str">
         <v>T:2026-08-28|T:09:40:00</v>
       </c>
       <c r="E765" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="766">
@@ -60898,16 +61395,16 @@
         <v>766</v>
       </c>
       <c r="B766" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C766">
-        <v>236</v>
+        <v>766</v>
       </c>
       <c r="D766" t="str">
         <v>T:2026-08-28|T:10:03:00</v>
       </c>
       <c r="E766" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="767">
@@ -60915,16 +61412,16 @@
         <v>767</v>
       </c>
       <c r="B767" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C767">
-        <v>237</v>
+        <v>767</v>
       </c>
       <c r="D767" t="str">
         <v>T:2026-08-28|T:12:05:00</v>
       </c>
       <c r="E767" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="768">
@@ -60932,16 +61429,16 @@
         <v>768</v>
       </c>
       <c r="B768" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C768">
-        <v>238</v>
+        <v>768</v>
       </c>
       <c r="D768" t="str">
         <v>T:2026-08-28|T:13:55:00</v>
       </c>
       <c r="E768" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="769">
@@ -60949,16 +61446,16 @@
         <v>769</v>
       </c>
       <c r="B769" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C769">
-        <v>239</v>
+        <v>769</v>
       </c>
       <c r="D769" t="str">
         <v>T:2026-08-28|T:16:50:00</v>
       </c>
       <c r="E769" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="770">
@@ -60966,16 +61463,16 @@
         <v>770</v>
       </c>
       <c r="B770" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C770">
-        <v>240</v>
+        <v>770</v>
       </c>
       <c r="D770" t="str">
         <v>T:2026-08-28|T:18:49:00</v>
       </c>
       <c r="E770" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="771">
@@ -60983,16 +61480,16 @@
         <v>771</v>
       </c>
       <c r="B771" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C771">
-        <v>241</v>
+        <v>771</v>
       </c>
       <c r="D771" t="str">
         <v>T:2026-08-28|T:20:30:00</v>
       </c>
       <c r="E771" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="772">
@@ -61000,16 +61497,16 @@
         <v>772</v>
       </c>
       <c r="B772" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C772">
-        <v>242</v>
+        <v>772</v>
       </c>
       <c r="D772" t="str">
         <v>T:2026-08-29|T:01:00:00</v>
       </c>
       <c r="E772" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="773">
@@ -61017,16 +61514,16 @@
         <v>773</v>
       </c>
       <c r="B773" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C773">
-        <v>243</v>
+        <v>773</v>
       </c>
       <c r="D773" t="str">
         <v>T:2026-08-29|T:04:10:00</v>
       </c>
       <c r="E773" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="774">
@@ -61034,16 +61531,16 @@
         <v>774</v>
       </c>
       <c r="B774" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C774">
-        <v>244</v>
+        <v>774</v>
       </c>
       <c r="D774" t="str">
         <v>T:2026-08-29|T:05:45:00</v>
       </c>
       <c r="E774" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="775">
@@ -61051,16 +61548,16 @@
         <v>775</v>
       </c>
       <c r="B775" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C775">
-        <v>245</v>
+        <v>775</v>
       </c>
       <c r="D775" t="str">
         <v>T:2026-08-29|T:06:20:00</v>
       </c>
       <c r="E775" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="776">
@@ -61068,16 +61565,16 @@
         <v>776</v>
       </c>
       <c r="B776" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C776">
-        <v>246</v>
+        <v>776</v>
       </c>
       <c r="D776" t="str">
         <v>T:2026-08-29|T:08:26:00</v>
       </c>
       <c r="E776" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="777">
@@ -61085,16 +61582,16 @@
         <v>777</v>
       </c>
       <c r="B777" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C777">
-        <v>247</v>
+        <v>777</v>
       </c>
       <c r="D777" t="str">
         <v>T:2026-08-29|T:11:33:00</v>
       </c>
       <c r="E777" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="778">
@@ -61102,16 +61599,16 @@
         <v>778</v>
       </c>
       <c r="B778" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C778">
-        <v>248</v>
+        <v>778</v>
       </c>
       <c r="D778" t="str">
         <v>T:2026-08-29|T:12:10:00</v>
       </c>
       <c r="E778" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="779">
@@ -61119,16 +61616,16 @@
         <v>779</v>
       </c>
       <c r="B779" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C779">
-        <v>261</v>
+        <v>779</v>
       </c>
       <c r="D779" t="str">
         <v>T:2026-08-29|T:12:37:00</v>
       </c>
       <c r="E779" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="780">
@@ -61136,16 +61633,16 @@
         <v>780</v>
       </c>
       <c r="B780" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C780">
-        <v>249</v>
+        <v>780</v>
       </c>
       <c r="D780" t="str">
         <v>T:2026-08-29|T:15:24:00</v>
       </c>
       <c r="E780" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="781">
@@ -61153,16 +61650,16 @@
         <v>781</v>
       </c>
       <c r="B781" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C781">
-        <v>250</v>
+        <v>781</v>
       </c>
       <c r="D781" t="str">
         <v>T:2026-08-29|T:17:30:00</v>
       </c>
       <c r="E781" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="782">
@@ -61170,16 +61667,16 @@
         <v>782</v>
       </c>
       <c r="B782" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C782">
-        <v>258</v>
+        <v>782</v>
       </c>
       <c r="D782" t="str">
         <v>T:2026-08-29|T:18:10:00</v>
       </c>
       <c r="E782" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="783">
@@ -61187,16 +61684,16 @@
         <v>783</v>
       </c>
       <c r="B783" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C783">
-        <v>251</v>
+        <v>783</v>
       </c>
       <c r="D783" t="str">
         <v>T:2026-08-29|T:18:15:00</v>
       </c>
       <c r="E783" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="784">
@@ -61204,16 +61701,16 @@
         <v>784</v>
       </c>
       <c r="B784" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C784">
-        <v>252</v>
+        <v>784</v>
       </c>
       <c r="D784" t="str">
         <v>T:2026-08-29|T:19:20:00</v>
       </c>
       <c r="E784" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="785">
@@ -61221,16 +61718,16 @@
         <v>785</v>
       </c>
       <c r="B785" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C785">
-        <v>253</v>
+        <v>785</v>
       </c>
       <c r="D785" t="str">
         <v>T:2026-08-29|T:20:10:00</v>
       </c>
       <c r="E785" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="786">
@@ -61238,16 +61735,16 @@
         <v>786</v>
       </c>
       <c r="B786" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C786">
-        <v>259</v>
+        <v>786</v>
       </c>
       <c r="D786" t="str">
         <v>T:2026-08-29|T:20:25:00</v>
       </c>
       <c r="E786" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="787">
@@ -61255,16 +61752,16 @@
         <v>787</v>
       </c>
       <c r="B787" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C787">
-        <v>260</v>
+        <v>787</v>
       </c>
       <c r="D787" t="str">
         <v>T:2026-08-29|T:22:20:00</v>
       </c>
       <c r="E787" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="788">
@@ -61272,16 +61769,16 @@
         <v>788</v>
       </c>
       <c r="B788" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C788">
-        <v>254</v>
+        <v>788</v>
       </c>
       <c r="D788" t="str">
         <v>T:2026-08-29|T:22:22:00</v>
       </c>
       <c r="E788" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="789">
@@ -61289,16 +61786,16 @@
         <v>789</v>
       </c>
       <c r="B789" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C789">
-        <v>255</v>
+        <v>789</v>
       </c>
       <c r="D789" t="str">
         <v>T:2026-08-30|T:00:32:00</v>
       </c>
       <c r="E789" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="790">
@@ -61306,16 +61803,16 @@
         <v>790</v>
       </c>
       <c r="B790" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C790">
-        <v>256</v>
+        <v>790</v>
       </c>
       <c r="D790" t="str">
         <v>T:2026-08-30|T:02:30:00</v>
       </c>
       <c r="E790" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="791">
@@ -61323,16 +61820,16 @@
         <v>791</v>
       </c>
       <c r="B791" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C791">
-        <v>257</v>
+        <v>791</v>
       </c>
       <c r="D791" t="str">
         <v>T:2026-08-30|T:04:40:00</v>
       </c>
       <c r="E791" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="792">
@@ -61340,16 +61837,16 @@
         <v>792</v>
       </c>
       <c r="B792" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C792">
-        <v>262</v>
+        <v>792</v>
       </c>
       <c r="D792" t="str">
         <v>T:2026-08-30|T:16:18:00</v>
       </c>
       <c r="E792" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="793">
@@ -61357,16 +61854,16 @@
         <v>793</v>
       </c>
       <c r="B793" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C793">
-        <v>263</v>
+        <v>793</v>
       </c>
       <c r="D793" t="str">
         <v>T:2026-08-30|T:18:35:00</v>
       </c>
       <c r="E793" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="794">
@@ -61374,16 +61871,16 @@
         <v>794</v>
       </c>
       <c r="B794" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C794">
-        <v>264</v>
+        <v>794</v>
       </c>
       <c r="D794" t="str">
         <v>T:2026-08-30|T:20:00:00</v>
       </c>
       <c r="E794" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="795">
@@ -61391,16 +61888,16 @@
         <v>795</v>
       </c>
       <c r="B795" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C795">
-        <v>265</v>
+        <v>795</v>
       </c>
       <c r="D795" t="str">
         <v>T:2026-08-30|T:22:22:00</v>
       </c>
       <c r="E795" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="796">
@@ -61408,16 +61905,16 @@
         <v>796</v>
       </c>
       <c r="B796" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C796">
-        <v>267</v>
+        <v>796</v>
       </c>
       <c r="D796" t="str">
         <v>T:2026-08-31|T:00:20:00</v>
       </c>
       <c r="E796" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="797">
@@ -61425,16 +61922,16 @@
         <v>797</v>
       </c>
       <c r="B797" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C797">
-        <v>266</v>
+        <v>797</v>
       </c>
       <c r="D797" t="str">
         <v>T:2026-08-31|T:02:22:00</v>
       </c>
       <c r="E797" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="798">
@@ -61442,16 +61939,16 @@
         <v>798</v>
       </c>
       <c r="B798" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C798">
-        <v>268</v>
+        <v>798</v>
       </c>
       <c r="D798" t="str">
         <v>T:2026-08-31|T:04:44:00</v>
       </c>
       <c r="E798" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="799">
@@ -61459,16 +61956,16 @@
         <v>799</v>
       </c>
       <c r="B799" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C799">
-        <v>269</v>
+        <v>799</v>
       </c>
       <c r="D799" t="str">
         <v>T:2026-08-31|T:06:30:00</v>
       </c>
       <c r="E799" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="800">
@@ -61476,16 +61973,16 @@
         <v>800</v>
       </c>
       <c r="B800" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C800">
-        <v>270</v>
+        <v>800</v>
       </c>
       <c r="D800" t="str">
         <v>T:2026-08-31|T:08:15:00</v>
       </c>
       <c r="E800" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="801">
@@ -61493,16 +61990,16 @@
         <v>801</v>
       </c>
       <c r="B801" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C801">
-        <v>271</v>
+        <v>801</v>
       </c>
       <c r="D801" t="str">
         <v>T:2026-08-31|T:11:35:00</v>
       </c>
       <c r="E801" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="802">
@@ -61510,16 +62007,16 @@
         <v>802</v>
       </c>
       <c r="B802" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C802">
-        <v>272</v>
+        <v>802</v>
       </c>
       <c r="D802" t="str">
         <v>T:2026-08-31|T:15:33:00</v>
       </c>
       <c r="E802" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="803">
@@ -61527,16 +62024,16 @@
         <v>803</v>
       </c>
       <c r="B803" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C803">
-        <v>273</v>
+        <v>803</v>
       </c>
       <c r="D803" t="str">
         <v>T:2026-08-31|T:18:55:00</v>
       </c>
       <c r="E803" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="804">
@@ -61544,16 +62041,16 @@
         <v>804</v>
       </c>
       <c r="B804" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C804">
-        <v>274</v>
+        <v>804</v>
       </c>
       <c r="D804" t="str">
         <v>T:2026-08-31|T:20:31:00</v>
       </c>
       <c r="E804" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="805">
@@ -61561,16 +62058,16 @@
         <v>805</v>
       </c>
       <c r="B805" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C805">
-        <v>275</v>
+        <v>805</v>
       </c>
       <c r="D805" t="str">
         <v>T:2026-08-31|T:22:36:00</v>
       </c>
       <c r="E805" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="806">
@@ -61578,16 +62075,16 @@
         <v>806</v>
       </c>
       <c r="B806" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C806">
-        <v>283</v>
+        <v>806</v>
       </c>
       <c r="D806" t="str">
         <v>T:2026-09-01|T:01:05:00</v>
       </c>
       <c r="E806" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="807">
@@ -61595,16 +62092,16 @@
         <v>807</v>
       </c>
       <c r="B807" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C807">
-        <v>276</v>
+        <v>807</v>
       </c>
       <c r="D807" t="str">
         <v>T:2026-09-01|T:01:31:00</v>
       </c>
       <c r="E807" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="808">
@@ -61612,16 +62109,16 @@
         <v>808</v>
       </c>
       <c r="B808" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C808">
-        <v>277</v>
+        <v>808</v>
       </c>
       <c r="D808" t="str">
         <v>T:2026-09-01|T:03:24:00</v>
       </c>
       <c r="E808" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="809">
@@ -61629,16 +62126,16 @@
         <v>809</v>
       </c>
       <c r="B809" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C809">
-        <v>278</v>
+        <v>809</v>
       </c>
       <c r="D809" t="str">
         <v>T:2026-09-01|T:05:34:00</v>
       </c>
       <c r="E809" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="810">
@@ -61646,16 +62143,16 @@
         <v>810</v>
       </c>
       <c r="B810" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C810">
-        <v>279</v>
+        <v>810</v>
       </c>
       <c r="D810" t="str">
         <v>T:2026-09-01|T:06:23:00</v>
       </c>
       <c r="E810" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="811">
@@ -61663,16 +62160,16 @@
         <v>811</v>
       </c>
       <c r="B811" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C811">
-        <v>281</v>
+        <v>811</v>
       </c>
       <c r="D811" t="str">
         <v>T:2026-09-01|T:08:00:00</v>
       </c>
       <c r="E811" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="812">
@@ -61680,16 +62177,16 @@
         <v>812</v>
       </c>
       <c r="B812" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C812">
-        <v>282</v>
+        <v>812</v>
       </c>
       <c r="D812" t="str">
         <v>T:2026-09-01|T:10:39:00</v>
       </c>
       <c r="E812" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="813">
@@ -61697,16 +62194,16 @@
         <v>813</v>
       </c>
       <c r="B813" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C813">
-        <v>284</v>
+        <v>813</v>
       </c>
       <c r="D813" t="str">
         <v>T:2026-09-01|T:15:43:00</v>
       </c>
       <c r="E813" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="814">
@@ -61714,16 +62211,16 @@
         <v>814</v>
       </c>
       <c r="B814" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C814">
-        <v>285</v>
+        <v>814</v>
       </c>
       <c r="D814" t="str">
         <v>T:2026-09-01|T:18:16:00</v>
       </c>
       <c r="E814" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="815">
@@ -61731,16 +62228,16 @@
         <v>815</v>
       </c>
       <c r="B815" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C815">
-        <v>280</v>
+        <v>815</v>
       </c>
       <c r="D815" t="str">
         <v>T:2026-09-01|T:20:00:00</v>
       </c>
       <c r="E815" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="816">
@@ -61748,16 +62245,16 @@
         <v>816</v>
       </c>
       <c r="B816" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C816">
-        <v>286</v>
+        <v>816</v>
       </c>
       <c r="D816" t="str">
         <v>T:2026-09-01|T:20:14:00</v>
       </c>
       <c r="E816" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="817">
@@ -61765,16 +62262,16 @@
         <v>817</v>
       </c>
       <c r="B817" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C817">
-        <v>287</v>
+        <v>817</v>
       </c>
       <c r="D817" t="str">
         <v>T:2026-09-01|T:22:33:00</v>
       </c>
       <c r="E817" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="818">
@@ -61782,16 +62279,16 @@
         <v>818</v>
       </c>
       <c r="B818" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C818">
-        <v>288</v>
+        <v>818</v>
       </c>
       <c r="D818" t="str">
         <v>T:2026-09-02|T:01:23:00</v>
       </c>
       <c r="E818" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="819">
@@ -61799,16 +62296,16 @@
         <v>819</v>
       </c>
       <c r="B819" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C819">
-        <v>289</v>
+        <v>819</v>
       </c>
       <c r="D819" t="str">
         <v>T:2026-09-02|T:03:23:00</v>
       </c>
       <c r="E819" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="820">
@@ -61816,16 +62313,16 @@
         <v>820</v>
       </c>
       <c r="B820" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C820">
-        <v>290</v>
+        <v>820</v>
       </c>
       <c r="D820" t="str">
         <v>T:2026-09-02|T:05:21:00</v>
       </c>
       <c r="E820" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="821">
@@ -61833,16 +62330,16 @@
         <v>821</v>
       </c>
       <c r="B821" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C821">
-        <v>291</v>
+        <v>821</v>
       </c>
       <c r="D821" t="str">
         <v>T:2026-09-02|T:06:52:00</v>
       </c>
       <c r="E821" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="822">
@@ -61850,16 +62347,16 @@
         <v>822</v>
       </c>
       <c r="B822" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C822">
-        <v>292</v>
+        <v>822</v>
       </c>
       <c r="D822" t="str">
         <v>T:2026-09-02|T:08:50:00</v>
       </c>
       <c r="E822" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="823">
@@ -61867,16 +62364,16 @@
         <v>823</v>
       </c>
       <c r="B823" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C823">
-        <v>293</v>
+        <v>823</v>
       </c>
       <c r="D823" t="str">
         <v>T:2026-09-02|T:11:48:00</v>
       </c>
       <c r="E823" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="824">
@@ -61884,16 +62381,16 @@
         <v>824</v>
       </c>
       <c r="B824" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C824">
-        <v>294</v>
+        <v>824</v>
       </c>
       <c r="D824" t="str">
         <v>T:2026-09-02|T:16:30:00</v>
       </c>
       <c r="E824" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="825">
@@ -61901,16 +62398,16 @@
         <v>825</v>
       </c>
       <c r="B825" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C825">
-        <v>295</v>
+        <v>825</v>
       </c>
       <c r="D825" t="str">
         <v>T:2026-09-02|T:17:25:00</v>
       </c>
       <c r="E825" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="826">
@@ -61918,16 +62415,16 @@
         <v>826</v>
       </c>
       <c r="B826" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C826">
-        <v>296</v>
+        <v>826</v>
       </c>
       <c r="D826" t="str">
         <v>T:2026-09-02|T:18:30:00</v>
       </c>
       <c r="E826" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="827">
@@ -61935,16 +62432,16 @@
         <v>827</v>
       </c>
       <c r="B827" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C827">
-        <v>297</v>
+        <v>827</v>
       </c>
       <c r="D827" t="str">
         <v>T:2026-09-02|T:21:13:00</v>
       </c>
       <c r="E827" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="828">
@@ -61952,16 +62449,16 @@
         <v>828</v>
       </c>
       <c r="B828" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C828">
-        <v>298</v>
+        <v>828</v>
       </c>
       <c r="D828" t="str">
         <v>T:2026-09-02|T:23:25:00</v>
       </c>
       <c r="E828" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="829">
@@ -61969,16 +62466,16 @@
         <v>829</v>
       </c>
       <c r="B829" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C829">
-        <v>299</v>
+        <v>829</v>
       </c>
       <c r="D829" t="str">
         <v>T:2026-09-03|T:01:34:00</v>
       </c>
       <c r="E829" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="830">
@@ -61986,16 +62483,16 @@
         <v>830</v>
       </c>
       <c r="B830" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C830">
-        <v>300</v>
+        <v>830</v>
       </c>
       <c r="D830" t="str">
         <v>T:2026-09-03|T:03:31:00</v>
       </c>
       <c r="E830" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="831">
@@ -62003,16 +62500,16 @@
         <v>831</v>
       </c>
       <c r="B831" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C831">
-        <v>301</v>
+        <v>831</v>
       </c>
       <c r="D831" t="str">
         <v>T:2026-09-03|T:05:00:00</v>
       </c>
       <c r="E831" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="832">
@@ -62020,16 +62517,16 @@
         <v>832</v>
       </c>
       <c r="B832" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C832">
-        <v>302</v>
+        <v>832</v>
       </c>
       <c r="D832" t="str">
         <v>T:2026-09-03|T:08:21:00</v>
       </c>
       <c r="E832" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="833">
@@ -62037,16 +62534,16 @@
         <v>833</v>
       </c>
       <c r="B833" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C833">
-        <v>303</v>
+        <v>833</v>
       </c>
       <c r="D833" t="str">
         <v>T:2026-09-03|T:11:00:00</v>
       </c>
       <c r="E833" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="834">
@@ -62054,16 +62551,16 @@
         <v>834</v>
       </c>
       <c r="B834" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C834">
-        <v>304</v>
+        <v>834</v>
       </c>
       <c r="D834" t="str">
         <v>T:2026-09-03|T:15:26:00</v>
       </c>
       <c r="E834" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="835">
@@ -62071,16 +62568,16 @@
         <v>835</v>
       </c>
       <c r="B835" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C835">
-        <v>305</v>
+        <v>835</v>
       </c>
       <c r="D835" t="str">
         <v>T:2026-09-03|T:17:57:00</v>
       </c>
       <c r="E835" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="836">
@@ -62088,16 +62585,16 @@
         <v>836</v>
       </c>
       <c r="B836" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C836">
-        <v>306</v>
+        <v>836</v>
       </c>
       <c r="D836" t="str">
         <v>T:2026-09-03|T:19:05:00</v>
       </c>
       <c r="E836" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="837">
@@ -62105,16 +62602,16 @@
         <v>837</v>
       </c>
       <c r="B837" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C837">
-        <v>307</v>
+        <v>837</v>
       </c>
       <c r="D837" t="str">
         <v>T:2026-09-03|T:21:01:00</v>
       </c>
       <c r="E837" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="838">
@@ -62122,16 +62619,16 @@
         <v>838</v>
       </c>
       <c r="B838" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C838">
-        <v>308</v>
+        <v>838</v>
       </c>
       <c r="D838" t="str">
         <v>T:2026-09-03|T:23:09:00</v>
       </c>
       <c r="E838" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="839">
@@ -62139,16 +62636,16 @@
         <v>839</v>
       </c>
       <c r="B839" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C839">
-        <v>309</v>
+        <v>839</v>
       </c>
       <c r="D839" t="str">
         <v>T:2026-09-04|T:01:16:00</v>
       </c>
       <c r="E839" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="840">
@@ -62156,16 +62653,16 @@
         <v>840</v>
       </c>
       <c r="B840" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C840">
-        <v>310</v>
+        <v>840</v>
       </c>
       <c r="D840" t="str">
         <v>T:2026-09-04|T:03:27:00</v>
       </c>
       <c r="E840" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="841">
@@ -62173,16 +62670,16 @@
         <v>841</v>
       </c>
       <c r="B841" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C841">
-        <v>311</v>
+        <v>841</v>
       </c>
       <c r="D841" t="str">
         <v>T:2026-09-04|T:05:22:00</v>
       </c>
       <c r="E841" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="842">
@@ -62190,16 +62687,16 @@
         <v>842</v>
       </c>
       <c r="B842" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C842">
-        <v>312</v>
+        <v>842</v>
       </c>
       <c r="D842" t="str">
         <v>T:2026-09-04|T:07:31:00</v>
       </c>
       <c r="E842" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="843">
@@ -62207,16 +62704,16 @@
         <v>843</v>
       </c>
       <c r="B843" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C843">
-        <v>313</v>
+        <v>843</v>
       </c>
       <c r="D843" t="str">
         <v>T:2026-09-04|T:09:30:00</v>
       </c>
       <c r="E843" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="844">
@@ -62224,16 +62721,16 @@
         <v>844</v>
       </c>
       <c r="B844" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C844">
-        <v>314</v>
+        <v>844</v>
       </c>
       <c r="D844" t="str">
         <v>T:2026-09-04|T:13:10:00</v>
       </c>
       <c r="E844" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="845">
@@ -62241,16 +62738,16 @@
         <v>845</v>
       </c>
       <c r="B845" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C845">
-        <v>315</v>
+        <v>845</v>
       </c>
       <c r="D845" t="str">
         <v>T:2026-09-04|T:15:35:00</v>
       </c>
       <c r="E845" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="846">
@@ -62258,16 +62755,16 @@
         <v>846</v>
       </c>
       <c r="B846" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C846">
-        <v>316</v>
+        <v>846</v>
       </c>
       <c r="D846" t="str">
         <v>T:2026-09-04|T:18:23:00</v>
       </c>
       <c r="E846" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="847">
@@ -62275,16 +62772,16 @@
         <v>847</v>
       </c>
       <c r="B847" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C847">
-        <v>317</v>
+        <v>847</v>
       </c>
       <c r="D847" t="str">
         <v>T:2026-09-04|T:19:48:00</v>
       </c>
       <c r="E847" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="848">
@@ -62292,16 +62789,16 @@
         <v>848</v>
       </c>
       <c r="B848" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C848">
-        <v>318</v>
+        <v>848</v>
       </c>
       <c r="D848" t="str">
         <v>T:2026-09-04|T:22:41:00</v>
       </c>
       <c r="E848" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="849">
@@ -62309,16 +62806,16 @@
         <v>849</v>
       </c>
       <c r="B849" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C849">
-        <v>319</v>
+        <v>849</v>
       </c>
       <c r="D849" t="str">
         <v>T:2026-09-05|T:01:05:00</v>
       </c>
       <c r="E849" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="850">
@@ -62326,16 +62823,16 @@
         <v>850</v>
       </c>
       <c r="B850" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C850">
-        <v>320</v>
+        <v>850</v>
       </c>
       <c r="D850" t="str">
         <v>T:2026-09-05|T:05:00:00</v>
       </c>
       <c r="E850" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="851">
@@ -62343,16 +62840,16 @@
         <v>851</v>
       </c>
       <c r="B851" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C851">
-        <v>321</v>
+        <v>851</v>
       </c>
       <c r="D851" t="str">
         <v>T:2026-09-05|T:07:02:00</v>
       </c>
       <c r="E851" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="852">
@@ -62360,16 +62857,16 @@
         <v>852</v>
       </c>
       <c r="B852" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C852">
-        <v>322</v>
+        <v>852</v>
       </c>
       <c r="D852" t="str">
         <v>T:2026-09-05|T:09:05:00</v>
       </c>
       <c r="E852" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="853">
@@ -62377,16 +62874,16 @@
         <v>853</v>
       </c>
       <c r="B853" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C853">
-        <v>323</v>
+        <v>853</v>
       </c>
       <c r="D853" t="str">
         <v>T:2026-09-05|T:11:36:00</v>
       </c>
       <c r="E853" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="854">
@@ -62394,16 +62891,16 @@
         <v>854</v>
       </c>
       <c r="B854" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C854">
-        <v>324</v>
+        <v>854</v>
       </c>
       <c r="D854" t="str">
         <v>T:2026-09-05|T:13:38:00</v>
       </c>
       <c r="E854" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="855">
@@ -62411,16 +62908,16 @@
         <v>855</v>
       </c>
       <c r="B855" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C855">
-        <v>329</v>
+        <v>855</v>
       </c>
       <c r="D855" t="str">
         <v>T:2026-09-05|T:14:06:00</v>
       </c>
       <c r="E855" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="856">
@@ -62428,16 +62925,16 @@
         <v>856</v>
       </c>
       <c r="B856" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C856">
-        <v>325</v>
+        <v>856</v>
       </c>
       <c r="D856" t="str">
         <v>T:2026-09-05|T:15:56:00</v>
       </c>
       <c r="E856" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="857">
@@ -62445,16 +62942,16 @@
         <v>857</v>
       </c>
       <c r="B857" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C857">
-        <v>330</v>
+        <v>857</v>
       </c>
       <c r="D857" t="str">
         <v>T:2026-09-05|T:16:30:00</v>
       </c>
       <c r="E857" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="858">
@@ -62462,16 +62959,16 @@
         <v>858</v>
       </c>
       <c r="B858" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C858">
-        <v>326</v>
+        <v>858</v>
       </c>
       <c r="D858" t="str">
         <v>T:2026-09-05|T:17:27:00</v>
       </c>
       <c r="E858" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="859">
@@ -62479,16 +62976,16 @@
         <v>859</v>
       </c>
       <c r="B859" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C859">
-        <v>327</v>
+        <v>859</v>
       </c>
       <c r="D859" t="str">
         <v>T:2026-09-05|T:20:22:00</v>
       </c>
       <c r="E859" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="860">
@@ -62496,16 +62993,16 @@
         <v>860</v>
       </c>
       <c r="B860" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C860">
-        <v>328</v>
+        <v>860</v>
       </c>
       <c r="D860" t="str">
         <v>T:2026-09-05|T:23:12:00</v>
       </c>
       <c r="E860" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="861">
@@ -62513,16 +63010,16 @@
         <v>861</v>
       </c>
       <c r="B861" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C861">
-        <v>331</v>
+        <v>861</v>
       </c>
       <c r="D861" t="str">
         <v>T:2026-09-06|T:07:17:00</v>
       </c>
       <c r="E861" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="862">
@@ -62530,16 +63027,16 @@
         <v>862</v>
       </c>
       <c r="B862" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C862">
-        <v>332</v>
+        <v>862</v>
       </c>
       <c r="D862" t="str">
         <v>T:2026-09-06|T:09:42:00</v>
       </c>
       <c r="E862" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="863">
@@ -62547,16 +63044,16 @@
         <v>863</v>
       </c>
       <c r="B863" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C863">
-        <v>333</v>
+        <v>863</v>
       </c>
       <c r="D863" t="str">
         <v>T:2026-09-06|T:12:36:00</v>
       </c>
       <c r="E863" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="864">
@@ -62564,16 +63061,16 @@
         <v>864</v>
       </c>
       <c r="B864" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C864">
-        <v>334</v>
+        <v>864</v>
       </c>
       <c r="D864" t="str">
         <v>T:2026-09-06|T:14:53:00</v>
       </c>
       <c r="E864" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="865">
@@ -62581,16 +63078,16 @@
         <v>865</v>
       </c>
       <c r="B865" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C865">
-        <v>335</v>
+        <v>865</v>
       </c>
       <c r="D865" t="str">
         <v>T:2026-09-06|T:19:12:00</v>
       </c>
       <c r="E865" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="866">
@@ -62598,16 +63095,16 @@
         <v>866</v>
       </c>
       <c r="B866" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C866">
-        <v>336</v>
+        <v>866</v>
       </c>
       <c r="D866" t="str">
         <v>T:2026-09-06|T:20:55:00</v>
       </c>
       <c r="E866" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="867">
@@ -62615,16 +63112,16 @@
         <v>867</v>
       </c>
       <c r="B867" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C867">
-        <v>337</v>
+        <v>867</v>
       </c>
       <c r="D867" t="str">
         <v>T:2026-09-07|T:00:46:00</v>
       </c>
       <c r="E867" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="868">
@@ -62632,16 +63129,16 @@
         <v>868</v>
       </c>
       <c r="B868" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C868">
-        <v>338</v>
+        <v>868</v>
       </c>
       <c r="D868" t="str">
         <v>T:2026-09-07|T:02:57:00</v>
       </c>
       <c r="E868" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="869">
@@ -62649,16 +63146,16 @@
         <v>869</v>
       </c>
       <c r="B869" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C869">
-        <v>339</v>
+        <v>869</v>
       </c>
       <c r="D869" t="str">
         <v>T:2026-09-07|T:05:23:00</v>
       </c>
       <c r="E869" t="str">
-        <v>Exclusivo secundaria</v>
+        <v>Base principal</v>
       </c>
     </row>
     <row r="870">
@@ -62666,21 +63163,140 @@
         <v>870</v>
       </c>
       <c r="B870" t="str">
-        <v>Secundaria</v>
+        <v>Principal</v>
       </c>
       <c r="C870">
-        <v>340</v>
+        <v>870</v>
       </c>
       <c r="D870" t="str">
         <v>T:2026-09-07|T:07:39:00</v>
       </c>
       <c r="E870" t="str">
+        <v>Base principal</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871">
+        <v>871</v>
+      </c>
+      <c r="B871" t="str">
+        <v>Secundaria</v>
+      </c>
+      <c r="C871">
+        <v>2</v>
+      </c>
+      <c r="D871" t="str">
+        <v>T:2026-09-07|T:12:36:00</v>
+      </c>
+      <c r="E871" t="str">
+        <v>Exclusivo secundaria</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872">
+        <v>872</v>
+      </c>
+      <c r="B872" t="str">
+        <v>Secundaria</v>
+      </c>
+      <c r="C872">
+        <v>3</v>
+      </c>
+      <c r="D872" t="str">
+        <v>T:2026-09-07|T:15:04:00</v>
+      </c>
+      <c r="E872" t="str">
+        <v>Exclusivo secundaria</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873">
+        <v>873</v>
+      </c>
+      <c r="B873" t="str">
+        <v>Secundaria</v>
+      </c>
+      <c r="C873">
+        <v>4</v>
+      </c>
+      <c r="D873" t="str">
+        <v>T:2026-09-07|T:16:51:00</v>
+      </c>
+      <c r="E873" t="str">
+        <v>Exclusivo secundaria</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874">
+        <v>874</v>
+      </c>
+      <c r="B874" t="str">
+        <v>Secundaria</v>
+      </c>
+      <c r="C874">
+        <v>5</v>
+      </c>
+      <c r="D874" t="str">
+        <v>T:2026-09-07|T:20:07:00</v>
+      </c>
+      <c r="E874" t="str">
+        <v>Exclusivo secundaria</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875">
+        <v>875</v>
+      </c>
+      <c r="B875" t="str">
+        <v>Secundaria</v>
+      </c>
+      <c r="C875">
+        <v>6</v>
+      </c>
+      <c r="D875" t="str">
+        <v>T:2026-09-07|T:23:50:00</v>
+      </c>
+      <c r="E875" t="str">
+        <v>Exclusivo secundaria</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876">
+        <v>876</v>
+      </c>
+      <c r="B876" t="str">
+        <v>Secundaria</v>
+      </c>
+      <c r="C876">
+        <v>7</v>
+      </c>
+      <c r="D876" t="str">
+        <v>T:2026-09-08|T:03:49:00</v>
+      </c>
+      <c r="E876" t="str">
+        <v>Exclusivo secundaria</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877">
+        <v>877</v>
+      </c>
+      <c r="B877" t="str">
+        <v>Secundaria</v>
+      </c>
+      <c r="C877">
+        <v>8</v>
+      </c>
+      <c r="D877" t="str">
+        <v>T:2026-09-08|T:05:25:00</v>
+      </c>
+      <c r="E877" t="str">
         <v>Exclusivo secundaria</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E870"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E877"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/registros.xlsx
+++ b/registros.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA877"/>
+  <dimension ref="A1:AA879"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -48374,9 +48374,151 @@
         <v>{"Hora":"05:25","Observaciones":"Ningúna ","Fecha":"2026-09-08","PlacaCisterna":"0","Encargado":"Edison Giraldo Isaza"}</v>
       </c>
     </row>
+    <row r="878">
+      <c r="A878">
+        <v>44</v>
+      </c>
+      <c r="B878">
+        <v>100</v>
+      </c>
+      <c r="C878">
+        <v>19</v>
+      </c>
+      <c r="D878">
+        <v>93</v>
+      </c>
+      <c r="E878">
+        <v>110</v>
+      </c>
+      <c r="F878">
+        <v>22</v>
+      </c>
+      <c r="G878">
+        <v>14826</v>
+      </c>
+      <c r="H878" t="str">
+        <v>Uzn256</v>
+      </c>
+      <c r="I878">
+        <v>115</v>
+      </c>
+      <c r="J878">
+        <v>56</v>
+      </c>
+      <c r="K878">
+        <v>110</v>
+      </c>
+      <c r="L878">
+        <v>10</v>
+      </c>
+      <c r="O878" t="str">
+        <v>Inicia trasiego</v>
+      </c>
+      <c r="P878" t="str">
+        <v>Jorge mario Cadavid gallego</v>
+      </c>
+      <c r="Q878" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="R878" t="str">
+        <v>06:14:00</v>
+      </c>
+      <c r="U878">
+        <v>1788873375834</v>
+      </c>
+      <c r="V878" t="str">
+        <v>2026-09-08T13:16:15.834Z</v>
+      </c>
+      <c r="W878" t="str">
+        <v>08/09/2026, 08:16:15</v>
+      </c>
+      <c r="X878">
+        <v>122</v>
+      </c>
+      <c r="Y878">
+        <v>11</v>
+      </c>
+      <c r="Z878">
+        <v>11</v>
+      </c>
+      <c r="AA878" t="str">
+        <v>{"Encargado":"Jorge mario Cadavid gallego","Hora":"06:14","Observaciones":"Inicia trasiego","PlacaCisterna":"Uzn256","Fecha":"2026-09-08"}</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879">
+        <v>85</v>
+      </c>
+      <c r="B879">
+        <v>100</v>
+      </c>
+      <c r="C879">
+        <v>19</v>
+      </c>
+      <c r="D879">
+        <v>44</v>
+      </c>
+      <c r="E879">
+        <v>110</v>
+      </c>
+      <c r="F879">
+        <v>22</v>
+      </c>
+      <c r="G879">
+        <v>14826</v>
+      </c>
+      <c r="H879" t="str">
+        <v>Uzn256</v>
+      </c>
+      <c r="I879">
+        <v>115</v>
+      </c>
+      <c r="J879">
+        <v>56</v>
+      </c>
+      <c r="K879">
+        <v>110</v>
+      </c>
+      <c r="L879">
+        <v>12</v>
+      </c>
+      <c r="O879" t="str">
+        <v>Termina trasiego</v>
+      </c>
+      <c r="P879" t="str">
+        <v>Jorge mario Cadavid gallego</v>
+      </c>
+      <c r="Q879" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="R879" t="str">
+        <v>08:16:00</v>
+      </c>
+      <c r="U879">
+        <v>1788873500263</v>
+      </c>
+      <c r="V879" t="str">
+        <v>2026-09-08T13:18:20.263Z</v>
+      </c>
+      <c r="W879" t="str">
+        <v>08/09/2026, 08:18:20</v>
+      </c>
+      <c r="X879">
+        <v>2</v>
+      </c>
+      <c r="Y879">
+        <v>11</v>
+      </c>
+      <c r="Z879">
+        <v>11</v>
+      </c>
+      <c r="AA879" t="str">
+        <v>{"PlacaCisterna":"Uzn256","Hora":"08:16","Encargado":"Jorge mario Cadavid gallego","Observaciones":"Termina trasiego","Fecha":"2026-09-08"}</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA877"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA879"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/registros.xlsx
+++ b/registros.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA879"/>
+  <dimension ref="A1:AA880"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -48516,9 +48516,80 @@
         <v>{"PlacaCisterna":"Uzn256","Hora":"08:16","Encargado":"Jorge mario Cadavid gallego","Observaciones":"Termina trasiego","Fecha":"2026-09-08"}</v>
       </c>
     </row>
+    <row r="880">
+      <c r="A880">
+        <v>66</v>
+      </c>
+      <c r="B880">
+        <v>100</v>
+      </c>
+      <c r="C880">
+        <v>19</v>
+      </c>
+      <c r="D880">
+        <v>44</v>
+      </c>
+      <c r="E880">
+        <v>110</v>
+      </c>
+      <c r="F880">
+        <v>22</v>
+      </c>
+      <c r="G880">
+        <v>14826</v>
+      </c>
+      <c r="H880" t="str">
+        <v>Uzn256</v>
+      </c>
+      <c r="I880">
+        <v>110</v>
+      </c>
+      <c r="J880">
+        <v>56</v>
+      </c>
+      <c r="K880">
+        <v>110</v>
+      </c>
+      <c r="L880">
+        <v>12</v>
+      </c>
+      <c r="O880" t="str">
+        <v>Ninguna</v>
+      </c>
+      <c r="P880" t="str">
+        <v>Jorge mario Cadavid gallego</v>
+      </c>
+      <c r="Q880" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="R880" t="str">
+        <v>13:16:00</v>
+      </c>
+      <c r="U880">
+        <v>1788891488888</v>
+      </c>
+      <c r="V880" t="str">
+        <v>2026-09-08T18:18:08.888Z</v>
+      </c>
+      <c r="W880" t="str">
+        <v>08/09/2026, 13:18:08</v>
+      </c>
+      <c r="X880">
+        <v>2</v>
+      </c>
+      <c r="Y880">
+        <v>11</v>
+      </c>
+      <c r="Z880">
+        <v>11</v>
+      </c>
+      <c r="AA880" t="str">
+        <v>{"Encargado":"Jorge mario Cadavid gallego","Fecha":"2026-09-08","Hora":"13:16","Observaciones":"Ninguna","PlacaCisterna":"Uzn256"}</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA879"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA880"/>
   </ignoredErrors>
 </worksheet>
 </file>
